--- a/PUEYRREDON 1494/Junio/PUEYRREDON JUNIO.xlsx
+++ b/PUEYRREDON 1494/Junio/PUEYRREDON JUNIO.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\OneDrive\Desktop\RC CONSORCIO 2025\PUEYRREDON 1494\Junio\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{934F4FB2-8CDA-49B3-8C3E-136284797F64}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7FA0B8FE-EC7D-427E-BF08-DC4449B83F75}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" tabRatio="793" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" tabRatio="793" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="RESUMEN" sheetId="1" r:id="rId1"/>
@@ -18,14 +18,14 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm.Print_Area" localSheetId="1">PRORRATEO!$A$1:$P$34</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="0">RESUMEN!$A$1:$E$110</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="0">RESUMEN!$A$1:$E$112</definedName>
   </definedNames>
   <calcPr calcId="181029"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="180" uniqueCount="161">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="183" uniqueCount="165">
   <si>
     <t>MAIL: consorciopueyrredon1494@gmail.com</t>
   </si>
@@ -114,15 +114,9 @@
     <t xml:space="preserve">ARCA </t>
   </si>
   <si>
-    <t>PMC 06/05</t>
-  </si>
-  <si>
     <t>Suther</t>
   </si>
   <si>
-    <t>Debito 13/05</t>
-  </si>
-  <si>
     <t>Fathery</t>
   </si>
   <si>
@@ -135,24 +129,12 @@
     <t>ABONOS Y SERVICIOS</t>
   </si>
   <si>
-    <t>Transf 16/05</t>
-  </si>
-  <si>
-    <t>Mantenimiento Ascensores - Mes de MAYO</t>
-  </si>
-  <si>
     <t xml:space="preserve">Edesur </t>
   </si>
   <si>
-    <t>Debito 05/05</t>
-  </si>
-  <si>
     <t>Metrogas</t>
   </si>
   <si>
-    <t>PMC 07/05</t>
-  </si>
-  <si>
     <t>TOTAL ABONOS Y SERVICIOS</t>
   </si>
   <si>
@@ -177,12 +159,6 @@
     <t>GASTOS EXTRAORDINARIOS UNIDADES FUNCIONALES:</t>
   </si>
   <si>
-    <t>Cuota 3/9 arreglo terraza Sr. Luis (Total a abonar $1.250.000) - No se prorratea ya que se previsiono</t>
-  </si>
-  <si>
-    <t>Camara de seguridad Imou Ipc-f22p-d</t>
-  </si>
-  <si>
     <t>PREVISION EXTRAORDINARIA</t>
   </si>
   <si>
@@ -508,6 +484,42 @@
   </si>
   <si>
     <t>Efect 12/06</t>
+  </si>
+  <si>
+    <t>Debito 04/06</t>
+  </si>
+  <si>
+    <t>Transf 30/06</t>
+  </si>
+  <si>
+    <t>Debito 12/06</t>
+  </si>
+  <si>
+    <t>PMC 10/06</t>
+  </si>
+  <si>
+    <t>Transf 11/06</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Seguro de vida </t>
+  </si>
+  <si>
+    <t>Reemplazo Vacaciones Mirtha - Sra. Gisela</t>
+  </si>
+  <si>
+    <t>PMC 07/06</t>
+  </si>
+  <si>
+    <t>METROGAS LO VENIMOS DIBUJANDO HACE 1 MES - HAY QUE ARREGLARLO</t>
+  </si>
+  <si>
+    <t>DEBEMOS MANTENIMIENTO DE ASCENSORES JUN</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4/9 arreglo terraza Sr. Luis (Total a abonar $1.250.000) </t>
+  </si>
+  <si>
+    <t>DEPOSITA SIEMPRE VALERIA</t>
   </si>
 </sst>
 </file>
@@ -1152,7 +1164,7 @@
     <xf numFmtId="165" fontId="1" fillId="0" borderId="0"/>
     <xf numFmtId="43" fontId="1" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="186">
+  <cellXfs count="183">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="16" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -1355,17 +1367,26 @@
     <xf numFmtId="0" fontId="23" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="19" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="18" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="9" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="9" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="27" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="22" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="28" xfId="0" applyBorder="1"/>
@@ -1379,26 +1400,26 @@
     <xf numFmtId="0" fontId="23" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="13" fillId="3" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="19" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="13" fillId="3" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="20" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="3" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="13" fillId="3" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="18" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="19" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="13" fillId="3" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="3" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="20" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="13" fillId="3" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -1416,25 +1437,9 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="3" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="3" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="8" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="166" fontId="8" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="166" fontId="8" fillId="2" borderId="6" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="23" fillId="9" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
+    <xf numFmtId="164" fontId="25" fillId="11" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
+    <xf numFmtId="166" fontId="4" fillId="2" borderId="6" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="4">
     <cellStyle name="Millares" xfId="3" builtinId="3"/>
@@ -1742,7 +1747,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:M114"/>
+  <dimension ref="A1:M116"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="37.5703125" customWidth="1"/>
@@ -1808,7 +1813,7 @@
         <v>6</v>
       </c>
       <c r="B6" s="20" t="s">
-        <v>153</v>
+        <v>145</v>
       </c>
       <c r="C6" s="17"/>
       <c r="D6" s="78" t="s">
@@ -1826,7 +1831,7 @@
       <c r="E7" s="21"/>
     </row>
     <row r="9" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="B9" s="162" t="s">
+      <c r="B9" s="150" t="s">
         <v>9</v>
       </c>
       <c r="C9" s="151"/>
@@ -1841,7 +1846,7 @@
     </row>
     <row r="13" spans="1:5" hidden="1" x14ac:dyDescent="0.25"/>
     <row r="14" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A14" s="163" t="s">
+      <c r="A14" s="154" t="s">
         <v>10</v>
       </c>
       <c r="B14" s="151"/>
@@ -1900,7 +1905,7 @@
       <c r="B23" s="5"/>
       <c r="C23" s="5"/>
       <c r="D23" s="137">
-        <v>769441.8</v>
+        <v>1292761.2</v>
       </c>
       <c r="E23" s="96"/>
     </row>
@@ -1911,7 +1916,7 @@
       <c r="B24" s="5"/>
       <c r="C24" s="5"/>
       <c r="D24" s="137">
-        <v>-168081.61</v>
+        <v>-281175.56</v>
       </c>
       <c r="E24" s="96"/>
     </row>
@@ -1922,7 +1927,7 @@
       <c r="B25" s="5"/>
       <c r="C25" s="5"/>
       <c r="D25" s="137">
-        <v>0.81</v>
+        <v>0.36</v>
       </c>
       <c r="E25" s="96"/>
       <c r="H25" s="22"/>
@@ -1943,759 +1948,768 @@
       <c r="C27" s="65"/>
       <c r="D27" s="138">
         <f>SUM(D23:D26)</f>
-        <v>601361.00000000012</v>
+        <v>1011585.9999999999</v>
       </c>
       <c r="E27" s="97"/>
       <c r="H27" s="5"/>
     </row>
-    <row r="28" spans="1:8" ht="14.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A28" s="30" t="s">
+    <row r="28" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A28" s="5" t="s">
+        <v>159</v>
+      </c>
+      <c r="B28" s="5"/>
+      <c r="C28" s="5"/>
+      <c r="D28" s="137">
+        <v>300000</v>
+      </c>
+      <c r="E28" s="96"/>
+      <c r="H28" s="22"/>
+    </row>
+    <row r="29" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A29" s="5" t="s">
+        <v>158</v>
+      </c>
+      <c r="B29" s="5"/>
+      <c r="C29" s="5"/>
+      <c r="D29" s="137">
+        <v>10989</v>
+      </c>
+      <c r="E29" s="96"/>
+      <c r="H29" s="5"/>
+    </row>
+    <row r="30" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A30" s="65" t="s">
+        <v>16</v>
+      </c>
+      <c r="B30" s="65"/>
+      <c r="C30" s="65"/>
+      <c r="D30" s="180">
+        <f>SUM(D28:D29)</f>
+        <v>310989</v>
+      </c>
+      <c r="E30" s="97"/>
+      <c r="H30" s="181"/>
+    </row>
+    <row r="31" spans="1:8" ht="14.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A31" s="30" t="s">
         <v>17</v>
       </c>
-      <c r="B28" s="30"/>
-      <c r="C28" s="30"/>
-      <c r="D28" s="139"/>
-      <c r="E28" s="98">
-        <f>D27</f>
-        <v>601361.00000000012</v>
-      </c>
-      <c r="F28" s="22"/>
-    </row>
-    <row r="29" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A29" s="40" t="s">
+      <c r="B31" s="30"/>
+      <c r="C31" s="30"/>
+      <c r="D31" s="139"/>
+      <c r="E31" s="98">
+        <f>D27+D30</f>
+        <v>1322575</v>
+      </c>
+      <c r="F31" s="22"/>
+    </row>
+    <row r="32" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A32" s="40" t="s">
         <v>18</v>
       </c>
-      <c r="B29" s="40"/>
-      <c r="C29" s="40"/>
-      <c r="D29" s="140"/>
-      <c r="E29" s="99"/>
-    </row>
-    <row r="30" spans="1:8" ht="28.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A30" s="72" t="s">
+      <c r="B32" s="40"/>
+      <c r="C32" s="40"/>
+      <c r="D32" s="140"/>
+      <c r="E32" s="99"/>
+    </row>
+    <row r="33" spans="1:7" ht="28.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A33" s="72" t="s">
         <v>19</v>
       </c>
-      <c r="B30" s="5" t="s">
+      <c r="B33" s="5" t="s">
         <v>21</v>
       </c>
-      <c r="C30" s="5"/>
-      <c r="D30" s="180">
+      <c r="C33" s="5"/>
+      <c r="D33" s="137">
         <v>35000</v>
       </c>
-      <c r="E30" s="100"/>
-    </row>
-    <row r="31" spans="1:8" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A31" s="5" t="s">
+      <c r="E33" s="100"/>
+    </row>
+    <row r="34" spans="1:7" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A34" s="5" t="s">
         <v>20</v>
       </c>
-      <c r="B31" s="5" t="s">
-        <v>154</v>
-      </c>
-      <c r="C31" s="5"/>
-      <c r="D31" s="137">
+      <c r="B34" s="5" t="s">
+        <v>146</v>
+      </c>
+      <c r="C34" s="5"/>
+      <c r="D34" s="137">
         <v>120000</v>
       </c>
-      <c r="E31" s="100"/>
-    </row>
-    <row r="32" spans="1:8" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A32" s="30" t="s">
+      <c r="E34" s="100"/>
+    </row>
+    <row r="35" spans="1:7" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A35" s="30" t="s">
         <v>22</v>
       </c>
-      <c r="B32" s="30"/>
-      <c r="C32" s="30"/>
-      <c r="D32" s="141"/>
-      <c r="E32" s="101">
-        <f>SUM(D30:D31)</f>
+      <c r="B35" s="30"/>
+      <c r="C35" s="30"/>
+      <c r="D35" s="141"/>
+      <c r="E35" s="101">
+        <f>SUM(D33:D34)</f>
         <v>155000</v>
       </c>
     </row>
-    <row r="33" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A33" s="38" t="s">
+    <row r="36" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A36" s="38" t="s">
         <v>23</v>
       </c>
-      <c r="B33" s="39"/>
-      <c r="C33" s="39"/>
-      <c r="D33" s="142"/>
-      <c r="E33" s="74"/>
-    </row>
-    <row r="34" spans="1:7" s="44" customFormat="1" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A34" s="164" t="s">
+      <c r="B36" s="39"/>
+      <c r="C36" s="39"/>
+      <c r="D36" s="142"/>
+      <c r="E36" s="74"/>
+    </row>
+    <row r="37" spans="1:7" s="44" customFormat="1" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A37" s="155" t="s">
         <v>24</v>
       </c>
-      <c r="B34" s="154"/>
-      <c r="C34" s="63"/>
-      <c r="D34" s="143">
+      <c r="B37" s="153"/>
+      <c r="C37" s="63"/>
+      <c r="D37" s="143">
         <v>87562.7</v>
       </c>
-      <c r="E34" s="122"/>
-    </row>
-    <row r="35" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A35" s="164" t="s">
+      <c r="E37" s="122"/>
+    </row>
+    <row r="38" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A38" s="155" t="s">
         <v>25</v>
       </c>
-      <c r="B35" s="154"/>
-      <c r="C35" s="63"/>
-      <c r="D35" s="144">
+      <c r="B38" s="153"/>
+      <c r="C38" s="63"/>
+      <c r="D38" s="144">
         <v>6646.91</v>
       </c>
-      <c r="E35" s="122"/>
-    </row>
-    <row r="36" spans="1:7" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A36" s="30" t="s">
+      <c r="E38" s="122"/>
+    </row>
+    <row r="39" spans="1:7" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A39" s="30" t="s">
         <v>26</v>
       </c>
-      <c r="B36" s="30"/>
-      <c r="C36" s="30"/>
-      <c r="D36" s="141"/>
-      <c r="E36" s="102">
-        <f>SUM(D34:D35)</f>
+      <c r="B39" s="30"/>
+      <c r="C39" s="30"/>
+      <c r="D39" s="141"/>
+      <c r="E39" s="102">
+        <f>SUM(D37:D38)</f>
         <v>94209.61</v>
       </c>
     </row>
-    <row r="37" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A37" s="40" t="s">
+    <row r="40" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A40" s="40" t="s">
         <v>27</v>
       </c>
-      <c r="B37" s="31"/>
-      <c r="C37" s="31"/>
-      <c r="D37" s="145"/>
-      <c r="E37" s="103"/>
-    </row>
-    <row r="38" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A38" s="5" t="s">
+      <c r="B40" s="31"/>
+      <c r="C40" s="31"/>
+      <c r="D40" s="145"/>
+      <c r="E40" s="103"/>
+    </row>
+    <row r="41" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A41" s="5" t="s">
         <v>28</v>
       </c>
-      <c r="B38" s="5"/>
-      <c r="C38" s="61"/>
-      <c r="D38" s="144">
-        <v>371131.27</v>
-      </c>
-      <c r="E38" s="123" t="s">
+      <c r="B41" s="5"/>
+      <c r="C41" s="61"/>
+      <c r="D41" s="144">
+        <v>371183.27</v>
+      </c>
+      <c r="E41" s="123" t="s">
+        <v>156</v>
+      </c>
+      <c r="G41" s="120"/>
+    </row>
+    <row r="42" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A42" s="5" t="s">
+        <v>147</v>
+      </c>
+      <c r="B42" s="5" t="s">
         <v>29</v>
       </c>
-      <c r="G38" s="120"/>
-    </row>
-    <row r="39" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A39" s="5" t="s">
+      <c r="C42" s="5"/>
+      <c r="D42" s="144">
+        <v>19236.05</v>
+      </c>
+      <c r="E42" s="124" t="s">
         <v>155</v>
       </c>
-      <c r="B39" s="5" t="s">
+    </row>
+    <row r="43" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A43" s="5" t="str">
+        <f>A42</f>
+        <v>Sindicatos mes de JUNIO</v>
+      </c>
+      <c r="B43" s="5" t="s">
         <v>30</v>
       </c>
-      <c r="C39" s="5"/>
-      <c r="D39" s="144">
-        <v>19236.05</v>
-      </c>
-      <c r="E39" s="124" t="s">
+      <c r="C43" s="5"/>
+      <c r="D43" s="144">
+        <v>62013.71</v>
+      </c>
+      <c r="E43" s="124" t="str">
+        <f>E42</f>
+        <v>Debito 12/06</v>
+      </c>
+    </row>
+    <row r="44" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A44" s="5" t="str">
+        <f>A43</f>
+        <v>Sindicatos mes de JUNIO</v>
+      </c>
+      <c r="B44" s="5" t="s">
         <v>31</v>
       </c>
-    </row>
-    <row r="40" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A40" s="5" t="str">
-        <f>A39</f>
-        <v>Sindicatos mes de JUNIO</v>
-      </c>
-      <c r="B40" s="5" t="s">
-        <v>32</v>
-      </c>
-      <c r="C40" s="5"/>
-      <c r="D40" s="144">
-        <v>62013.71</v>
-      </c>
-      <c r="E40" s="124" t="str">
-        <f>E39</f>
-        <v>Debito 13/05</v>
-      </c>
-    </row>
-    <row r="41" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A41" s="5" t="str">
-        <f>A40</f>
-        <v>Sindicatos mes de JUNIO</v>
-      </c>
-      <c r="B41" s="5" t="s">
-        <v>33</v>
-      </c>
-      <c r="C41" s="5"/>
-      <c r="D41" s="144">
-        <v>3847.21</v>
-      </c>
-      <c r="E41" s="125" t="str">
-        <f>E40</f>
-        <v>Debito 13/05</v>
-      </c>
-    </row>
-    <row r="42" spans="1:7" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A42" s="30" t="s">
-        <v>34</v>
-      </c>
-      <c r="B42" s="31"/>
-      <c r="C42" s="31"/>
-      <c r="D42" s="146"/>
-      <c r="E42" s="102">
-        <f>SUM(D38:D41)</f>
-        <v>456228.24000000005</v>
-      </c>
-    </row>
-    <row r="43" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A43" s="40" t="s">
-        <v>35</v>
-      </c>
-      <c r="B43" s="31"/>
-      <c r="C43" s="31"/>
-      <c r="D43" s="145"/>
-      <c r="E43" s="103"/>
-    </row>
-    <row r="44" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A44" s="61" t="s">
-        <v>37</v>
-      </c>
-      <c r="B44" s="5"/>
       <c r="C44" s="5"/>
       <c r="D44" s="144">
-        <v>33360</v>
-      </c>
-      <c r="E44" s="106" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="45" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A45" s="61" t="s">
-        <v>156</v>
-      </c>
-      <c r="B45" s="5"/>
-      <c r="C45" s="5"/>
-      <c r="D45" s="144">
-        <v>36700</v>
-      </c>
-      <c r="E45" s="106" t="s">
-        <v>36</v>
-      </c>
-      <c r="G45" s="128"/>
-    </row>
-    <row r="46" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A46" s="5" t="s">
-        <v>38</v>
-      </c>
-      <c r="B46" s="5"/>
-      <c r="C46" s="5"/>
-      <c r="D46" s="183">
-        <v>69753.66</v>
-      </c>
-      <c r="E46" s="185" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="47" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A47" s="5" t="s">
-        <v>40</v>
+        <v>3847.21</v>
+      </c>
+      <c r="E44" s="125" t="str">
+        <f>E43</f>
+        <v>Debito 12/06</v>
+      </c>
+    </row>
+    <row r="45" spans="1:7" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A45" s="30" t="s">
+        <v>32</v>
+      </c>
+      <c r="B45" s="31"/>
+      <c r="C45" s="31"/>
+      <c r="D45" s="146"/>
+      <c r="E45" s="102">
+        <f>SUM(D41:D44)</f>
+        <v>456280.24000000005</v>
+      </c>
+    </row>
+    <row r="46" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A46" s="40" t="s">
+        <v>33</v>
+      </c>
+      <c r="B46" s="31"/>
+      <c r="C46" s="31"/>
+      <c r="D46" s="145"/>
+      <c r="E46" s="103"/>
+    </row>
+    <row r="47" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A47" s="61" t="s">
+        <v>148</v>
       </c>
       <c r="B47" s="5"/>
       <c r="C47" s="5"/>
-      <c r="D47" s="144">
-        <v>25000</v>
-      </c>
-      <c r="E47" s="106" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="48" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="D47" s="144"/>
+      <c r="E47" s="106"/>
+      <c r="G47" s="128" t="s">
+        <v>162</v>
+      </c>
+    </row>
+    <row r="48" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A48" s="5" t="s">
-        <v>159</v>
+        <v>34</v>
       </c>
       <c r="B48" s="5"/>
       <c r="C48" s="5"/>
-      <c r="D48" s="183">
-        <v>25000</v>
+      <c r="D48" s="144">
+        <v>69753.66</v>
       </c>
       <c r="E48" s="106" t="s">
-        <v>160</v>
+        <v>153</v>
       </c>
     </row>
     <row r="49" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A49" s="61" t="s">
-        <v>158</v>
+      <c r="A49" s="5" t="s">
+        <v>35</v>
       </c>
       <c r="B49" s="5"/>
       <c r="C49" s="5"/>
-      <c r="D49" s="183">
+      <c r="D49" s="144">
+        <v>25000</v>
+      </c>
+      <c r="E49" s="106" t="s">
+        <v>160</v>
+      </c>
+      <c r="G49" t="s">
+        <v>161</v>
+      </c>
+    </row>
+    <row r="50" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A50" s="5" t="s">
+        <v>151</v>
+      </c>
+      <c r="B50" s="5"/>
+      <c r="C50" s="5"/>
+      <c r="D50" s="144">
+        <v>25000</v>
+      </c>
+      <c r="E50" s="106" t="s">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="51" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A51" s="61" t="s">
+        <v>150</v>
+      </c>
+      <c r="B51" s="5"/>
+      <c r="C51" s="5"/>
+      <c r="D51" s="144">
         <v>1000000</v>
       </c>
-      <c r="E49" s="185" t="s">
+      <c r="E51" s="106" t="s">
+        <v>154</v>
+      </c>
+    </row>
+    <row r="52" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A52" s="152" t="s">
+        <v>149</v>
+      </c>
+      <c r="B52" s="153"/>
+      <c r="C52" s="64"/>
+      <c r="D52" s="182">
+        <v>54750</v>
+      </c>
+      <c r="E52" s="124" t="s">
+        <v>157</v>
+      </c>
+    </row>
+    <row r="53" spans="1:7" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A53" s="30" t="s">
         <v>36</v>
       </c>
-    </row>
-    <row r="50" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A50" s="181" t="s">
-        <v>157</v>
-      </c>
-      <c r="B50" s="182"/>
-      <c r="C50" s="64"/>
-      <c r="D50" s="184">
-        <v>54750</v>
-      </c>
-      <c r="E50" s="104"/>
-    </row>
-    <row r="51" spans="1:7" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A51" s="30" t="s">
-        <v>42</v>
-      </c>
-      <c r="B51" s="30"/>
-      <c r="C51" s="30"/>
-      <c r="D51" s="141"/>
-      <c r="E51" s="102">
-        <f>SUM(D44:D50)</f>
-        <v>1244563.6599999999</v>
-      </c>
-    </row>
-    <row r="52" spans="1:7" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A52" s="40" t="s">
-        <v>43</v>
-      </c>
-      <c r="B52" s="30"/>
-      <c r="C52" s="30"/>
-      <c r="D52" s="141"/>
-      <c r="E52" s="105"/>
-    </row>
-    <row r="53" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A53" s="61"/>
-      <c r="B53" s="5"/>
-      <c r="C53" s="5"/>
-      <c r="D53" s="42"/>
-      <c r="E53" s="104"/>
+      <c r="B53" s="30"/>
+      <c r="C53" s="30"/>
+      <c r="D53" s="141"/>
+      <c r="E53" s="102">
+        <f>SUM(D47:D52)</f>
+        <v>1174503.6599999999</v>
+      </c>
     </row>
     <row r="54" spans="1:7" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A54" s="30" t="s">
-        <v>44</v>
-      </c>
-      <c r="B54" s="40"/>
-      <c r="C54" s="40"/>
-      <c r="D54" s="38"/>
-      <c r="E54" s="108">
-        <f>SUM(D53:D53)</f>
+      <c r="A54" s="40" t="s">
+        <v>37</v>
+      </c>
+      <c r="B54" s="30"/>
+      <c r="C54" s="30"/>
+      <c r="D54" s="141"/>
+      <c r="E54" s="105"/>
+    </row>
+    <row r="55" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A55" s="61"/>
+      <c r="B55" s="5"/>
+      <c r="C55" s="5"/>
+      <c r="D55" s="42"/>
+      <c r="E55" s="104"/>
+    </row>
+    <row r="56" spans="1:7" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A56" s="30" t="s">
+        <v>38</v>
+      </c>
+      <c r="B56" s="40"/>
+      <c r="C56" s="40"/>
+      <c r="D56" s="38"/>
+      <c r="E56" s="108">
+        <f>SUM(D55:D55)</f>
         <v>0</v>
       </c>
     </row>
-    <row r="55" spans="1:7" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A55" s="40" t="s">
-        <v>45</v>
-      </c>
-      <c r="B55" s="73"/>
-      <c r="C55" s="30"/>
-      <c r="D55" s="139"/>
-      <c r="E55" s="105"/>
-    </row>
-    <row r="56" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A56" s="5" t="s">
-        <v>45</v>
-      </c>
-      <c r="B56" s="5"/>
-      <c r="C56" s="5"/>
-      <c r="D56" s="144">
-        <v>47733.48</v>
-      </c>
-      <c r="E56" s="109"/>
-    </row>
-    <row r="57" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A57" s="5" t="s">
-        <v>46</v>
-      </c>
-      <c r="B57" s="5"/>
-      <c r="C57" s="5"/>
-      <c r="D57" s="144">
-        <v>49082</v>
-      </c>
-      <c r="E57" s="107"/>
-    </row>
-    <row r="58" spans="1:7" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A58" s="60" t="s">
-        <v>22</v>
-      </c>
-      <c r="B58" s="60"/>
-      <c r="C58" s="60"/>
-      <c r="D58" s="110"/>
-      <c r="E58" s="102">
-        <f>SUM(D56:D57)</f>
-        <v>96815.48000000001</v>
-      </c>
-    </row>
-    <row r="59" spans="1:7" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A59" s="5"/>
+    <row r="57" spans="1:7" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A57" s="40" t="s">
+        <v>39</v>
+      </c>
+      <c r="B57" s="73"/>
+      <c r="C57" s="30"/>
+      <c r="D57" s="139"/>
+      <c r="E57" s="105"/>
+    </row>
+    <row r="58" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A58" s="5" t="s">
+        <v>39</v>
+      </c>
+      <c r="B58" s="5"/>
+      <c r="C58" s="5"/>
+      <c r="D58" s="144">
+        <v>57039.4</v>
+      </c>
+      <c r="E58" s="109"/>
+    </row>
+    <row r="59" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A59" s="5" t="s">
+        <v>40</v>
+      </c>
       <c r="B59" s="5"/>
       <c r="C59" s="5"/>
-      <c r="D59" s="96"/>
-      <c r="E59" s="111"/>
+      <c r="D59" s="144">
+        <v>49082</v>
+      </c>
+      <c r="E59" s="107"/>
     </row>
     <row r="60" spans="1:7" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A60" s="33" t="s">
+      <c r="A60" s="60" t="s">
+        <v>22</v>
+      </c>
+      <c r="B60" s="60"/>
+      <c r="C60" s="60"/>
+      <c r="D60" s="110"/>
+      <c r="E60" s="102">
+        <f>SUM(D58:D59)</f>
+        <v>106121.4</v>
+      </c>
+    </row>
+    <row r="61" spans="1:7" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A61" s="5"/>
+      <c r="B61" s="5"/>
+      <c r="C61" s="5"/>
+      <c r="D61" s="96"/>
+      <c r="E61" s="111"/>
+    </row>
+    <row r="62" spans="1:7" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A62" s="33" t="s">
+        <v>41</v>
+      </c>
+      <c r="B62" s="33"/>
+      <c r="C62" s="33"/>
+      <c r="D62" s="112"/>
+      <c r="E62" s="113"/>
+    </row>
+    <row r="63" spans="1:7" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A63" s="1"/>
+      <c r="D63" s="114"/>
+      <c r="E63" s="115"/>
+      <c r="F63" s="51"/>
+    </row>
+    <row r="64" spans="1:7" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A64" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="B64" s="10"/>
+      <c r="C64" s="4"/>
+      <c r="D64" s="116"/>
+      <c r="E64" s="117">
+        <f>(SUM(E31:E62))</f>
+        <v>3308689.9099999997</v>
+      </c>
+      <c r="F64" s="51"/>
+      <c r="G64" s="128"/>
+    </row>
+    <row r="65" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="D65" s="114"/>
+      <c r="E65" s="114"/>
+      <c r="G65" s="128"/>
+    </row>
+    <row r="66" spans="1:7" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="D66" s="114"/>
+      <c r="E66" s="114"/>
+    </row>
+    <row r="67" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A67" s="11" t="s">
+        <v>43</v>
+      </c>
+      <c r="B67" s="12"/>
+      <c r="C67" s="13"/>
+      <c r="D67" s="118"/>
+      <c r="E67" s="119"/>
+    </row>
+    <row r="68" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A68" s="152" t="s">
+        <v>163</v>
+      </c>
+      <c r="B68" s="158"/>
+      <c r="C68" s="5"/>
+      <c r="D68" s="162">
+        <v>181000</v>
+      </c>
+      <c r="E68" s="164"/>
+    </row>
+    <row r="69" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A69" s="159"/>
+      <c r="B69" s="160"/>
+      <c r="C69" s="61"/>
+      <c r="D69" s="163"/>
+      <c r="E69" s="163"/>
+    </row>
+    <row r="70" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A70" s="152"/>
+      <c r="B70" s="153"/>
+      <c r="C70" s="61"/>
+      <c r="D70" s="42"/>
+      <c r="E70" s="149"/>
+    </row>
+    <row r="71" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A71" s="58"/>
+      <c r="B71" s="57"/>
+      <c r="C71" s="57"/>
+      <c r="D71" s="66"/>
+      <c r="E71" s="66">
+        <f>SUM(D68:D70)</f>
+        <v>181000</v>
+      </c>
+    </row>
+    <row r="73" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A73" s="33" t="s">
+        <v>44</v>
+      </c>
+      <c r="B73" s="33"/>
+      <c r="C73" s="33"/>
+      <c r="D73" s="34"/>
+      <c r="E73" s="129"/>
+    </row>
+    <row r="74" spans="1:7" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="75" spans="1:7" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A75" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="B75" s="10"/>
+      <c r="C75" s="4"/>
+      <c r="D75" s="4"/>
+      <c r="E75" s="75">
+        <f>E71+E73</f>
+        <v>181000</v>
+      </c>
+    </row>
+    <row r="76" spans="1:7" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="77" spans="1:7" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A77" s="94" t="s">
+        <v>46</v>
+      </c>
+      <c r="B77" s="95">
+        <f>E64</f>
+        <v>3308689.9099999997</v>
+      </c>
+      <c r="D77" s="51"/>
+    </row>
+    <row r="78" spans="1:7" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A78" s="94" t="s">
         <v>47</v>
       </c>
-      <c r="B60" s="33"/>
-      <c r="C60" s="33"/>
-      <c r="D60" s="112"/>
-      <c r="E60" s="113"/>
-    </row>
-    <row r="61" spans="1:7" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A61" s="1"/>
-      <c r="D61" s="114"/>
-      <c r="E61" s="115"/>
-      <c r="F61" s="51"/>
-    </row>
-    <row r="62" spans="1:7" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A62" s="3" t="s">
+      <c r="B78" s="95">
+        <f>E64-E62</f>
+        <v>3308689.9099999997</v>
+      </c>
+    </row>
+    <row r="79" spans="1:7" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A79" s="94" t="s">
         <v>48</v>
       </c>
-      <c r="B62" s="10"/>
-      <c r="C62" s="4"/>
-      <c r="D62" s="116"/>
-      <c r="E62" s="117">
-        <f>(SUM(E28:E60))</f>
-        <v>2648177.9899999998</v>
-      </c>
-      <c r="F62" s="51"/>
-      <c r="G62" s="128"/>
-    </row>
-    <row r="63" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="D63" s="114"/>
-      <c r="E63" s="114"/>
-      <c r="G63" s="128"/>
-    </row>
-    <row r="64" spans="1:7" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="D64" s="114"/>
-      <c r="E64" s="114"/>
-    </row>
-    <row r="65" spans="1:5" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A65" s="11" t="s">
+      <c r="B79" s="95">
+        <f>E75-E73</f>
+        <v>181000</v>
+      </c>
+    </row>
+    <row r="80" spans="1:7" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A80" s="94" t="s">
         <v>49</v>
       </c>
-      <c r="B65" s="12"/>
-      <c r="C65" s="13"/>
-      <c r="D65" s="118"/>
-      <c r="E65" s="119"/>
-    </row>
-    <row r="66" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A66" s="153" t="s">
-        <v>50</v>
-      </c>
-      <c r="B66" s="155"/>
-      <c r="C66" s="5"/>
-      <c r="D66" s="159">
+      <c r="B80" s="95">
+        <f>E75</f>
         <v>181000</v>
       </c>
-      <c r="E66" s="161"/>
-    </row>
-    <row r="67" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A67" s="156"/>
-      <c r="B67" s="157"/>
-      <c r="C67" s="61"/>
-      <c r="D67" s="160"/>
-      <c r="E67" s="160"/>
-    </row>
-    <row r="68" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A68" s="153" t="s">
-        <v>51</v>
-      </c>
-      <c r="B68" s="154"/>
-      <c r="C68" s="61"/>
-      <c r="D68" s="42">
-        <v>47334</v>
-      </c>
-      <c r="E68" s="149"/>
-    </row>
-    <row r="69" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A69" s="58"/>
-      <c r="B69" s="57"/>
-      <c r="C69" s="57"/>
-      <c r="D69" s="66"/>
-      <c r="E69" s="66">
-        <f>SUM(D66:D68)</f>
-        <v>228334</v>
-      </c>
-    </row>
-    <row r="71" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A71" s="33" t="s">
-        <v>52</v>
-      </c>
-      <c r="B71" s="33"/>
-      <c r="C71" s="33"/>
-      <c r="D71" s="34"/>
-      <c r="E71" s="129"/>
-    </row>
-    <row r="72" spans="1:5" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3"/>
-    <row r="73" spans="1:5" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A73" s="3" t="s">
-        <v>53</v>
-      </c>
-      <c r="B73" s="10"/>
-      <c r="C73" s="4"/>
-      <c r="D73" s="4"/>
-      <c r="E73" s="75">
-        <f>E69+E71</f>
-        <v>228334</v>
-      </c>
-    </row>
-    <row r="74" spans="1:5" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3"/>
-    <row r="75" spans="1:5" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A75" s="94" t="s">
-        <v>54</v>
-      </c>
-      <c r="B75" s="95">
-        <f>E62</f>
-        <v>2648177.9899999998</v>
-      </c>
-      <c r="D75" s="51"/>
-    </row>
-    <row r="76" spans="1:5" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A76" s="94" t="s">
-        <v>55</v>
-      </c>
-      <c r="B76" s="95">
-        <f>E62-E60</f>
-        <v>2648177.9899999998</v>
-      </c>
-    </row>
-    <row r="77" spans="1:5" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A77" s="94" t="s">
-        <v>56</v>
-      </c>
-      <c r="B77" s="95">
-        <f>E73-E71</f>
-        <v>228334</v>
-      </c>
-    </row>
-    <row r="78" spans="1:5" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A78" s="94" t="s">
-        <v>57</v>
-      </c>
-      <c r="B78" s="95">
-        <f>E73</f>
-        <v>228334</v>
-      </c>
-    </row>
-    <row r="79" spans="1:5" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="80" spans="1:5" hidden="1" x14ac:dyDescent="0.25"/>
-    <row r="81" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A81" s="150"/>
-      <c r="B81" s="151"/>
-      <c r="C81" s="151"/>
-      <c r="D81" s="151"/>
-      <c r="E81" s="151"/>
-    </row>
-    <row r="82" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A82" s="151"/>
-      <c r="B82" s="151"/>
-      <c r="C82" s="151"/>
-      <c r="D82" s="151"/>
-      <c r="E82" s="151"/>
-    </row>
-    <row r="83" spans="1:5" ht="38.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A83" s="151"/>
+    </row>
+    <row r="81" spans="1:5" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="82" spans="1:5" hidden="1" x14ac:dyDescent="0.25"/>
+    <row r="83" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A83" s="156"/>
       <c r="B83" s="151"/>
       <c r="C83" s="151"/>
       <c r="D83" s="151"/>
       <c r="E83" s="151"/>
     </row>
-    <row r="85" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A85" s="23" t="s">
+    <row r="84" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A84" s="151"/>
+      <c r="B84" s="151"/>
+      <c r="C84" s="151"/>
+      <c r="D84" s="151"/>
+      <c r="E84" s="151"/>
+    </row>
+    <row r="85" spans="1:5" ht="38.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A85" s="151"/>
+      <c r="B85" s="151"/>
+      <c r="C85" s="151"/>
+      <c r="D85" s="151"/>
+      <c r="E85" s="151"/>
+    </row>
+    <row r="87" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A87" s="23" t="s">
+        <v>50</v>
+      </c>
+      <c r="B87" s="46"/>
+      <c r="C87" s="24"/>
+    </row>
+    <row r="88" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A88" s="36" t="s">
+        <v>51</v>
+      </c>
+      <c r="B88" s="127">
+        <v>-149600.7575000003</v>
+      </c>
+      <c r="C88" s="26"/>
+    </row>
+    <row r="89" spans="1:5" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A89" s="25" t="s">
+        <v>52</v>
+      </c>
+      <c r="B89" s="47">
+        <f>PRORRATEO!H25</f>
+        <v>2639132.91</v>
+      </c>
+      <c r="C89" s="24"/>
+    </row>
+    <row r="90" spans="1:5" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A90" s="25" t="s">
+        <v>53</v>
+      </c>
+      <c r="B90" s="55"/>
+      <c r="C90" s="24"/>
+    </row>
+    <row r="91" spans="1:5" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A91" s="133" t="s">
+        <v>54</v>
+      </c>
+      <c r="B91" s="55"/>
+      <c r="C91" s="24"/>
+    </row>
+    <row r="92" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A92" s="25" t="s">
+        <v>55</v>
+      </c>
+      <c r="B92" s="107">
+        <f>B111</f>
+        <v>0</v>
+      </c>
+      <c r="C92" s="24"/>
+    </row>
+    <row r="93" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A93" s="45" t="s">
+        <v>56</v>
+      </c>
+      <c r="B93" s="55">
+        <f>-B78</f>
+        <v>-3308689.9099999997</v>
+      </c>
+      <c r="C93" s="24"/>
+    </row>
+    <row r="94" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A94" s="28" t="s">
+        <v>57</v>
+      </c>
+      <c r="B94" s="55">
+        <f>-(B79)</f>
+        <v>-181000</v>
+      </c>
+      <c r="C94" s="24"/>
+    </row>
+    <row r="95" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A95" s="35" t="s">
+        <v>38</v>
+      </c>
+      <c r="B95" s="126">
+        <f>SUM(B88:B94)</f>
+        <v>-1000157.7574999998</v>
+      </c>
+      <c r="C95" s="27"/>
+    </row>
+    <row r="96" spans="1:5" ht="34.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B96" s="48"/>
+      <c r="C96" s="27"/>
+      <c r="D96" s="51"/>
+    </row>
+    <row r="97" spans="1:13" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B97" s="49"/>
+      <c r="C97" s="27"/>
+    </row>
+    <row r="98" spans="1:13" s="44" customFormat="1" ht="27" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B98" s="48"/>
+      <c r="C98" s="43"/>
+    </row>
+    <row r="99" spans="1:13" s="44" customFormat="1" ht="27" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A99" s="37" t="s">
         <v>58</v>
       </c>
-      <c r="B85" s="46"/>
-      <c r="C85" s="24"/>
-    </row>
-    <row r="86" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A86" s="36" t="s">
+      <c r="B99" s="41"/>
+      <c r="C99" s="43"/>
+      <c r="D99" s="54"/>
+    </row>
+    <row r="100" spans="1:13" s="44" customFormat="1" ht="27" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A100" s="5" t="s">
+        <v>51</v>
+      </c>
+      <c r="B100" s="42">
+        <v>0</v>
+      </c>
+      <c r="C100" s="43"/>
+    </row>
+    <row r="101" spans="1:13" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A101" s="5" t="s">
         <v>59</v>
-      </c>
-      <c r="B86" s="127">
-        <v>724965.22249999992</v>
-      </c>
-      <c r="C86" s="26"/>
-    </row>
-    <row r="87" spans="1:5" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A87" s="25" t="s">
-        <v>60</v>
-      </c>
-      <c r="B87" s="47">
-        <f>PRORRATEO!H25</f>
-        <v>1915682.4999999998</v>
-      </c>
-      <c r="C87" s="24"/>
-    </row>
-    <row r="88" spans="1:5" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A88" s="25" t="s">
-        <v>61</v>
-      </c>
-      <c r="B88" s="55"/>
-      <c r="C88" s="24"/>
-    </row>
-    <row r="89" spans="1:5" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A89" s="133" t="s">
-        <v>62</v>
-      </c>
-      <c r="B89" s="55"/>
-      <c r="C89" s="24"/>
-    </row>
-    <row r="90" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A90" s="25" t="s">
-        <v>63</v>
-      </c>
-      <c r="B90" s="107">
-        <f>B109</f>
-        <v>0</v>
-      </c>
-      <c r="C90" s="24"/>
-    </row>
-    <row r="91" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A91" s="45" t="s">
-        <v>64</v>
-      </c>
-      <c r="B91" s="55">
-        <f>-B76</f>
-        <v>-2648177.9899999998</v>
-      </c>
-      <c r="C91" s="24"/>
-    </row>
-    <row r="92" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A92" s="28" t="s">
-        <v>65</v>
-      </c>
-      <c r="B92" s="55">
-        <f>-(B77)</f>
-        <v>-228334</v>
-      </c>
-      <c r="C92" s="24"/>
-    </row>
-    <row r="93" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A93" s="35" t="s">
-        <v>44</v>
-      </c>
-      <c r="B93" s="126">
-        <f>SUM(B86:B92)</f>
-        <v>-235864.26750000007</v>
-      </c>
-      <c r="C93" s="27"/>
-    </row>
-    <row r="94" spans="1:5" ht="34.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B94" s="48"/>
-      <c r="C94" s="27"/>
-      <c r="D94" s="51"/>
-    </row>
-    <row r="95" spans="1:5" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B95" s="49"/>
-      <c r="C95" s="27"/>
-    </row>
-    <row r="96" spans="1:5" s="44" customFormat="1" ht="27" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B96" s="48"/>
-      <c r="C96" s="43"/>
-    </row>
-    <row r="97" spans="1:13" s="44" customFormat="1" ht="27" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A97" s="37" t="s">
-        <v>66</v>
-      </c>
-      <c r="B97" s="41"/>
-      <c r="C97" s="43"/>
-      <c r="D97" s="54"/>
-    </row>
-    <row r="98" spans="1:13" s="44" customFormat="1" ht="27" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A98" s="5" t="s">
-        <v>59</v>
-      </c>
-      <c r="B98" s="42">
-        <v>0</v>
-      </c>
-      <c r="C98" s="43"/>
-    </row>
-    <row r="99" spans="1:13" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A99" s="5" t="s">
-        <v>67</v>
-      </c>
-      <c r="B99" s="41">
-        <v>0</v>
-      </c>
-      <c r="C99" s="27"/>
-      <c r="D99" s="51"/>
-    </row>
-    <row r="100" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A100" s="5" t="s">
-        <v>64</v>
-      </c>
-      <c r="B100" s="41">
-        <v>0</v>
-      </c>
-      <c r="C100" s="27"/>
-    </row>
-    <row r="101" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A101" s="5" t="s">
-        <v>65</v>
       </c>
       <c r="B101" s="41">
         <v>0</v>
       </c>
-      <c r="C101" s="29"/>
+      <c r="C101" s="27"/>
+      <c r="D101" s="51"/>
     </row>
     <row r="102" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A102" s="37" t="s">
-        <v>68</v>
-      </c>
-      <c r="B102" s="56">
-        <f>SUM(B98:B101)</f>
+      <c r="A102" s="5" t="s">
+        <v>56</v>
+      </c>
+      <c r="B102" s="41">
         <v>0</v>
       </c>
-      <c r="C102" s="24"/>
-    </row>
-    <row r="103" spans="1:13" hidden="1" x14ac:dyDescent="0.25"/>
-    <row r="104" spans="1:13" ht="60.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="105" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A105" s="152" t="s">
-        <v>69</v>
-      </c>
-      <c r="B105" s="151"/>
-      <c r="C105" s="151"/>
-    </row>
-    <row r="106" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A106" s="151"/>
-      <c r="B106" s="151"/>
-      <c r="C106" s="151"/>
-    </row>
-    <row r="107" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A107" s="63"/>
-      <c r="B107" s="41"/>
-      <c r="C107" s="41">
+      <c r="C102" s="27"/>
+    </row>
+    <row r="103" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A103" s="5" t="s">
+        <v>57</v>
+      </c>
+      <c r="B103" s="41">
+        <v>0</v>
+      </c>
+      <c r="C103" s="29"/>
+    </row>
+    <row r="104" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A104" s="37" t="s">
+        <v>60</v>
+      </c>
+      <c r="B104" s="56">
+        <f>SUM(B100:B103)</f>
+        <v>0</v>
+      </c>
+      <c r="C104" s="24"/>
+    </row>
+    <row r="105" spans="1:13" hidden="1" x14ac:dyDescent="0.25"/>
+    <row r="106" spans="1:13" ht="60.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="107" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A107" s="157" t="s">
+        <v>61</v>
+      </c>
+      <c r="B107" s="151"/>
+      <c r="C107" s="151"/>
+    </row>
+    <row r="108" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A108" s="151"/>
+      <c r="B108" s="151"/>
+      <c r="C108" s="151"/>
+    </row>
+    <row r="109" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A109" s="63"/>
+      <c r="B109" s="41"/>
+      <c r="C109" s="41">
         <v>40000</v>
       </c>
     </row>
-    <row r="108" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A108" s="63"/>
-      <c r="B108" s="41"/>
-      <c r="C108" s="48"/>
-    </row>
-    <row r="109" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A109" s="52" t="s">
-        <v>44</v>
-      </c>
-      <c r="B109" s="121">
-        <f>SUM(B107:B108)</f>
+    <row r="110" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A110" s="63"/>
+      <c r="B110" s="41"/>
+      <c r="C110" s="48"/>
+    </row>
+    <row r="111" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A111" s="52" t="s">
+        <v>38</v>
+      </c>
+      <c r="B111" s="121">
+        <f>SUM(B109:B110)</f>
         <v>0</v>
       </c>
-      <c r="C109" s="53"/>
-    </row>
-    <row r="110" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="M110" s="8"/>
-    </row>
-    <row r="111" spans="1:13" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A111" s="158"/>
-      <c r="B111" s="151"/>
-      <c r="C111" s="151"/>
-      <c r="D111" s="151"/>
-      <c r="E111" s="151"/>
-    </row>
-    <row r="112" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A112" s="151"/>
-      <c r="B112" s="151"/>
-      <c r="C112" s="151"/>
-      <c r="D112" s="151"/>
-      <c r="E112" s="151"/>
-    </row>
-    <row r="113" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A113" s="151"/>
+      <c r="C111" s="53"/>
+    </row>
+    <row r="112" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="M112" s="8"/>
+    </row>
+    <row r="113" spans="1:5" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A113" s="161"/>
       <c r="B113" s="151"/>
       <c r="C113" s="151"/>
       <c r="D113" s="151"/>
@@ -2708,23 +2722,37 @@
       <c r="D114" s="151"/>
       <c r="E114" s="151"/>
     </row>
+    <row r="115" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A115" s="151"/>
+      <c r="B115" s="151"/>
+      <c r="C115" s="151"/>
+      <c r="D115" s="151"/>
+      <c r="E115" s="151"/>
+    </row>
+    <row r="116" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A116" s="151"/>
+      <c r="B116" s="151"/>
+      <c r="C116" s="151"/>
+      <c r="D116" s="151"/>
+      <c r="E116" s="151"/>
+    </row>
   </sheetData>
   <mergeCells count="12">
+    <mergeCell ref="A83:E85"/>
+    <mergeCell ref="A107:C108"/>
+    <mergeCell ref="A70:B70"/>
+    <mergeCell ref="A68:B69"/>
+    <mergeCell ref="A113:E116"/>
+    <mergeCell ref="D68:D69"/>
+    <mergeCell ref="E68:E69"/>
     <mergeCell ref="B9:C11"/>
-    <mergeCell ref="A50:B50"/>
+    <mergeCell ref="A52:B52"/>
     <mergeCell ref="A14:E17"/>
-    <mergeCell ref="A34:B34"/>
-    <mergeCell ref="A35:B35"/>
-    <mergeCell ref="A81:E83"/>
-    <mergeCell ref="A105:C106"/>
-    <mergeCell ref="A68:B68"/>
-    <mergeCell ref="A66:B67"/>
-    <mergeCell ref="A111:E114"/>
-    <mergeCell ref="D66:D67"/>
-    <mergeCell ref="E66:E67"/>
+    <mergeCell ref="A37:B37"/>
+    <mergeCell ref="A38:B38"/>
   </mergeCells>
   <pageMargins left="0.25" right="0.25" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>
 
@@ -2748,8 +2776,8 @@
     <col min="13" max="13" width="10.5703125" customWidth="1"/>
     <col min="14" max="14" width="10.5703125" hidden="1" customWidth="1"/>
     <col min="15" max="15" width="14" customWidth="1"/>
-    <col min="16" max="16" width="14.140625" customWidth="1"/>
-    <col min="17" max="17" width="7.42578125" hidden="1" customWidth="1"/>
+    <col min="16" max="16" width="13.5703125" customWidth="1"/>
+    <col min="17" max="17" width="4.42578125" hidden="1" customWidth="1"/>
     <col min="18" max="18" width="12" bestFit="1" customWidth="1"/>
     <col min="19" max="19" width="13" bestFit="1" customWidth="1"/>
   </cols>
@@ -2759,11 +2787,11 @@
       <c r="B1" s="6"/>
       <c r="C1" s="6"/>
       <c r="D1" s="6" t="s">
-        <v>70</v>
+        <v>62</v>
       </c>
       <c r="E1" s="6"/>
-      <c r="F1" s="177" t="s">
-        <v>71</v>
+      <c r="F1" s="169" t="s">
+        <v>63</v>
       </c>
       <c r="G1" s="151"/>
       <c r="H1" s="151"/>
@@ -2792,13 +2820,13 @@
       <c r="J2" s="6"/>
       <c r="K2" s="6"/>
       <c r="L2" s="7" t="s">
-        <v>72</v>
+        <v>64</v>
       </c>
       <c r="M2" s="6"/>
       <c r="N2" s="6"/>
-      <c r="O2" s="171">
+      <c r="O2" s="174">
         <f>T4</f>
-        <v>2609248.48</v>
+        <v>3000000</v>
       </c>
       <c r="P2" s="151"/>
       <c r="Q2" s="22"/>
@@ -2808,7 +2836,7 @@
       <c r="B3" s="6"/>
       <c r="C3" s="6"/>
       <c r="D3" s="6" t="s">
-        <v>73</v>
+        <v>65</v>
       </c>
       <c r="E3" s="6"/>
       <c r="F3" s="6"/>
@@ -2818,85 +2846,85 @@
       <c r="J3" s="6"/>
       <c r="K3" s="6"/>
       <c r="L3" s="7" t="s">
-        <v>74</v>
+        <v>66</v>
       </c>
       <c r="M3" s="6"/>
       <c r="N3" s="6"/>
-      <c r="O3" s="175">
+      <c r="O3" s="178">
         <f>S6</f>
-        <v>47334</v>
-      </c>
-      <c r="P3" s="176"/>
+        <v>181000</v>
+      </c>
+      <c r="P3" s="179"/>
     </row>
     <row r="4" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="A4" s="165" t="s">
+      <c r="A4" s="172" t="s">
+        <v>67</v>
+      </c>
+      <c r="B4" s="175" t="s">
+        <v>68</v>
+      </c>
+      <c r="C4" s="165" t="s">
+        <v>69</v>
+      </c>
+      <c r="D4" s="165" t="s">
+        <v>70</v>
+      </c>
+      <c r="E4" s="167" t="s">
+        <v>71</v>
+      </c>
+      <c r="F4" s="165" t="s">
+        <v>72</v>
+      </c>
+      <c r="G4" s="165" t="s">
+        <v>73</v>
+      </c>
+      <c r="H4" s="165" t="s">
+        <v>74</v>
+      </c>
+      <c r="I4" s="167" t="s">
         <v>75</v>
       </c>
-      <c r="B4" s="172" t="s">
+      <c r="J4" s="170" t="s">
         <v>76</v>
       </c>
-      <c r="C4" s="167" t="s">
+      <c r="K4" s="173" t="s">
         <v>77</v>
       </c>
-      <c r="D4" s="167" t="s">
+      <c r="L4" s="171" t="s">
         <v>78</v>
       </c>
-      <c r="E4" s="168" t="s">
+      <c r="M4" s="173" t="s">
         <v>79</v>
       </c>
-      <c r="F4" s="167" t="s">
+      <c r="N4" s="173" t="s">
         <v>80</v>
       </c>
-      <c r="G4" s="167" t="s">
+      <c r="O4" s="69" t="s">
         <v>81</v>
       </c>
-      <c r="H4" s="167" t="s">
+      <c r="P4" s="177" t="s">
         <v>82</v>
-      </c>
-      <c r="I4" s="168" t="s">
-        <v>83</v>
-      </c>
-      <c r="J4" s="178" t="s">
-        <v>84</v>
-      </c>
-      <c r="K4" s="170" t="s">
-        <v>85</v>
-      </c>
-      <c r="L4" s="179" t="s">
-        <v>86</v>
-      </c>
-      <c r="M4" s="170" t="s">
-        <v>87</v>
-      </c>
-      <c r="N4" s="170" t="s">
-        <v>88</v>
-      </c>
-      <c r="O4" s="69" t="s">
-        <v>89</v>
-      </c>
-      <c r="P4" s="174" t="s">
-        <v>90</v>
       </c>
       <c r="S4" s="51"/>
       <c r="T4">
-        <v>2609248.48</v>
+        <v>3000000</v>
       </c>
     </row>
     <row r="5" spans="1:20" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="166"/>
-      <c r="B5" s="173"/>
+      <c r="B5" s="176"/>
       <c r="C5" s="166"/>
       <c r="D5" s="166"/>
-      <c r="E5" s="169"/>
+      <c r="E5" s="168"/>
       <c r="F5" s="166"/>
       <c r="G5" s="166"/>
       <c r="H5" s="166"/>
-      <c r="I5" s="169"/>
-      <c r="J5" s="169"/>
-      <c r="K5" s="169"/>
+      <c r="I5" s="168"/>
+      <c r="J5" s="168"/>
+      <c r="K5" s="168"/>
       <c r="L5" s="166"/>
-      <c r="M5" s="169"/>
-      <c r="N5" s="169"/>
+      <c r="M5" s="168"/>
+      <c r="N5" s="168"/>
       <c r="O5" s="67" t="str">
         <f>RESUMEN!B9</f>
         <v>VTO 14/07</v>
@@ -2905,29 +2933,29 @@
     </row>
     <row r="6" spans="1:20" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="5" t="s">
-        <v>91</v>
+        <v>83</v>
       </c>
       <c r="B6" s="70">
         <v>1</v>
       </c>
       <c r="C6" s="70" t="s">
-        <v>92</v>
+        <v>84</v>
       </c>
       <c r="D6" s="70" t="s">
-        <v>93</v>
+        <v>85</v>
       </c>
       <c r="E6" s="70" t="s">
-        <v>94</v>
+        <v>86</v>
       </c>
       <c r="F6" s="80">
         <v>3</v>
       </c>
       <c r="G6" s="147">
-        <v>66000.100000000006</v>
+        <v>79697.100000000006</v>
       </c>
       <c r="H6" s="148">
         <f>G6</f>
-        <v>66000.100000000006</v>
+        <v>79697.100000000006</v>
       </c>
       <c r="I6" s="83"/>
       <c r="J6" s="134">
@@ -2940,62 +2968,61 @@
       </c>
       <c r="L6" s="85">
         <f t="shared" ref="L6:L24" si="2">O$3*F6%</f>
-        <v>1420.02</v>
+        <v>5430</v>
       </c>
       <c r="M6" s="85">
         <f t="shared" ref="M6:M24" si="3">O$2*F6%</f>
-        <v>78277.454400000002</v>
+        <v>90000</v>
       </c>
       <c r="N6" s="130">
         <f t="shared" ref="N6:N24" si="4">SUM(J6:M6)</f>
-        <v>79697.474400000006</v>
+        <v>95430</v>
       </c>
       <c r="O6" s="135" t="str">
         <f t="shared" ref="O6:O24" si="5">CONCATENATE("$",ROUND(N6,0), ",", Q6)</f>
-        <v>$79697,1</v>
+        <v>$95430,1</v>
       </c>
       <c r="P6" s="136" t="str">
         <f t="shared" ref="P6:P24" si="6">CONCATENATE("$",ROUND(N6*3%+ N6,0), ",", Q6)</f>
-        <v>$82088,1</v>
+        <v>$98293,1</v>
       </c>
       <c r="Q6" s="51" t="str">
         <f t="shared" ref="Q6:Q24" si="7">CONCATENATE(B6)</f>
         <v>1</v>
       </c>
       <c r="S6">
-        <v>47334</v>
+        <v>181000</v>
       </c>
     </row>
     <row r="7" spans="1:20" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="5" t="s">
-        <v>95</v>
+        <v>87</v>
       </c>
       <c r="B7" s="70">
         <v>2</v>
       </c>
       <c r="C7" s="70" t="s">
-        <v>96</v>
+        <v>88</v>
       </c>
       <c r="D7" s="70" t="s">
-        <v>97</v>
+        <v>89</v>
       </c>
       <c r="E7" s="70" t="s">
-        <v>98</v>
+        <v>90</v>
       </c>
       <c r="F7" s="80">
         <v>3.8</v>
       </c>
       <c r="G7" s="147">
-        <v>83600.2</v>
+        <v>100950.2</v>
       </c>
       <c r="H7" s="148">
-        <f>G7</f>
-        <v>83600.2</v>
+        <v>103979.02</v>
       </c>
       <c r="I7" s="83"/>
       <c r="J7" s="134">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>-3028.820000000007</v>
       </c>
       <c r="K7" s="84">
         <f t="shared" si="1"/>
@@ -3003,23 +3030,23 @@
       </c>
       <c r="L7" s="85">
         <f t="shared" si="2"/>
-        <v>1798.692</v>
+        <v>6878</v>
       </c>
       <c r="M7" s="85">
         <f t="shared" si="3"/>
-        <v>99151.442240000004</v>
+        <v>114000</v>
       </c>
       <c r="N7" s="130">
         <f t="shared" si="4"/>
-        <v>100950.13424</v>
+        <v>117849.18</v>
       </c>
       <c r="O7" s="132" t="str">
         <f t="shared" si="5"/>
-        <v>$100950,2</v>
+        <v>$117849,2</v>
       </c>
       <c r="P7" s="136" t="str">
         <f t="shared" si="6"/>
-        <v>$103979,2</v>
+        <v>$121385,2</v>
       </c>
       <c r="Q7" s="51" t="str">
         <f t="shared" si="7"/>
@@ -3029,29 +3056,29 @@
     </row>
     <row r="8" spans="1:20" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="5" t="s">
-        <v>95</v>
+        <v>87</v>
       </c>
       <c r="B8" s="70">
         <v>3</v>
       </c>
       <c r="C8" s="70" t="s">
-        <v>99</v>
+        <v>91</v>
       </c>
       <c r="D8" s="70" t="s">
-        <v>100</v>
+        <v>92</v>
       </c>
       <c r="E8" s="70" t="s">
-        <v>101</v>
+        <v>93</v>
       </c>
       <c r="F8" s="80">
         <v>3</v>
       </c>
       <c r="G8" s="147">
-        <v>66000.3</v>
+        <v>82088.3</v>
       </c>
       <c r="H8" s="148">
         <f>G8</f>
-        <v>66000.3</v>
+        <v>82088.3</v>
       </c>
       <c r="I8" s="83"/>
       <c r="J8" s="134">
@@ -3064,23 +3091,23 @@
       </c>
       <c r="L8" s="85">
         <f t="shared" si="2"/>
-        <v>1420.02</v>
+        <v>5430</v>
       </c>
       <c r="M8" s="85">
         <f t="shared" si="3"/>
-        <v>78277.454400000002</v>
+        <v>90000</v>
       </c>
       <c r="N8" s="130">
         <f t="shared" si="4"/>
-        <v>79697.474400000006</v>
+        <v>95430</v>
       </c>
       <c r="O8" s="132" t="str">
         <f t="shared" si="5"/>
-        <v>$79697,3</v>
+        <v>$95430,3</v>
       </c>
       <c r="P8" s="136" t="str">
         <f t="shared" si="6"/>
-        <v>$82088,3</v>
+        <v>$98293,3</v>
       </c>
       <c r="Q8" s="51" t="str">
         <f t="shared" si="7"/>
@@ -3089,55 +3116,57 @@
     </row>
     <row r="9" spans="1:20" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="5" t="s">
-        <v>102</v>
+        <v>94</v>
       </c>
       <c r="B9" s="70">
         <v>4</v>
       </c>
       <c r="C9" s="70" t="s">
-        <v>103</v>
+        <v>95</v>
       </c>
       <c r="D9" s="70" t="s">
-        <v>104</v>
+        <v>96</v>
       </c>
       <c r="E9" s="70" t="s">
-        <v>105</v>
+        <v>97</v>
       </c>
       <c r="F9" s="80">
         <v>3.1</v>
       </c>
       <c r="G9" s="147">
-        <v>146121.4</v>
-      </c>
-      <c r="H9" s="148"/>
+        <v>235782.39999999999</v>
+      </c>
+      <c r="H9" s="148">
+        <v>80000.039999999994</v>
+      </c>
       <c r="I9" s="83"/>
       <c r="J9" s="134">
         <f t="shared" si="0"/>
-        <v>146121.4</v>
+        <v>155782.35999999999</v>
       </c>
       <c r="K9" s="84">
         <f t="shared" si="1"/>
-        <v>7306.07</v>
+        <v>7789.1179999999995</v>
       </c>
       <c r="L9" s="85">
         <f t="shared" si="2"/>
-        <v>1467.354</v>
+        <v>5611</v>
       </c>
       <c r="M9" s="85">
         <f t="shared" si="3"/>
-        <v>80886.702879999997</v>
+        <v>93000</v>
       </c>
       <c r="N9" s="130">
         <f t="shared" si="4"/>
-        <v>235781.52687999999</v>
+        <v>262182.478</v>
       </c>
       <c r="O9" s="132" t="str">
         <f t="shared" si="5"/>
-        <v>$235782,4</v>
+        <v>$262182,4</v>
       </c>
       <c r="P9" s="136" t="str">
         <f t="shared" si="6"/>
-        <v>$242855,4</v>
+        <v>$270048,4</v>
       </c>
       <c r="Q9" s="51" t="str">
         <f t="shared" si="7"/>
@@ -3147,55 +3176,58 @@
     </row>
     <row r="10" spans="1:20" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="5" t="s">
-        <v>102</v>
+        <v>94</v>
       </c>
       <c r="B10" s="70">
         <v>5</v>
       </c>
       <c r="C10" s="70" t="s">
-        <v>106</v>
+        <v>98</v>
       </c>
       <c r="D10" s="70" t="s">
-        <v>107</v>
+        <v>99</v>
       </c>
       <c r="E10" s="70" t="s">
-        <v>108</v>
+        <v>100</v>
       </c>
       <c r="F10" s="80">
         <v>3.1</v>
       </c>
       <c r="G10" s="147">
-        <v>127229.5</v>
-      </c>
-      <c r="H10" s="148"/>
+        <v>224424.5</v>
+      </c>
+      <c r="H10" s="148">
+        <f>G10</f>
+        <v>224424.5</v>
+      </c>
       <c r="I10" s="83"/>
       <c r="J10" s="134">
         <f t="shared" si="0"/>
-        <v>127229.5</v>
+        <v>0</v>
       </c>
       <c r="K10" s="84">
         <f t="shared" si="1"/>
-        <v>6361.4750000000004</v>
+        <v>0</v>
       </c>
       <c r="L10" s="85">
         <f t="shared" si="2"/>
-        <v>1467.354</v>
+        <v>5611</v>
       </c>
       <c r="M10" s="85">
         <f t="shared" si="3"/>
-        <v>80886.702879999997</v>
+        <v>93000</v>
       </c>
       <c r="N10" s="130">
         <f t="shared" si="4"/>
-        <v>215945.03187999999</v>
+        <v>98611</v>
       </c>
       <c r="O10" s="132" t="str">
         <f t="shared" si="5"/>
-        <v>$215945,5</v>
+        <v>$98611,5</v>
       </c>
       <c r="P10" s="136" t="str">
         <f t="shared" si="6"/>
-        <v>$222423,5</v>
+        <v>$101569,5</v>
       </c>
       <c r="Q10" s="51" t="str">
         <f t="shared" si="7"/>
@@ -3205,31 +3237,32 @@
     </row>
     <row r="11" spans="1:20" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="5" t="s">
-        <v>109</v>
+        <v>101</v>
       </c>
       <c r="B11" s="70">
         <v>6</v>
       </c>
       <c r="C11" s="70" t="s">
-        <v>110</v>
+        <v>102</v>
       </c>
       <c r="D11" s="70" t="s">
-        <v>111</v>
+        <v>103</v>
       </c>
       <c r="E11" s="70"/>
       <c r="F11" s="80">
         <v>3.2</v>
       </c>
       <c r="G11" s="147">
-        <v>70400.600000000006</v>
+        <v>81011.600000000006</v>
       </c>
       <c r="H11" s="148">
-        <v>74400</v>
+        <f>G11</f>
+        <v>81011.600000000006</v>
       </c>
       <c r="I11" s="83"/>
       <c r="J11" s="134">
         <f t="shared" si="0"/>
-        <v>-3999.3999999999942</v>
+        <v>0</v>
       </c>
       <c r="K11" s="84">
         <f t="shared" si="1"/>
@@ -3237,23 +3270,23 @@
       </c>
       <c r="L11" s="85">
         <f t="shared" si="2"/>
-        <v>1514.6880000000001</v>
+        <v>5792</v>
       </c>
       <c r="M11" s="85">
         <f t="shared" si="3"/>
-        <v>83495.951360000006</v>
+        <v>96000</v>
       </c>
       <c r="N11" s="130">
         <f t="shared" si="4"/>
-        <v>81011.239360000007</v>
+        <v>101792</v>
       </c>
       <c r="O11" s="132" t="str">
         <f t="shared" si="5"/>
-        <v>$81011,6</v>
+        <v>$101792,6</v>
       </c>
       <c r="P11" s="136" t="str">
         <f t="shared" si="6"/>
-        <v>$83442,6</v>
+        <v>$104846,6</v>
       </c>
       <c r="Q11" s="51" t="str">
         <f t="shared" si="7"/>
@@ -3262,34 +3295,33 @@
     </row>
     <row r="12" spans="1:20" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="5" t="s">
-        <v>109</v>
+        <v>101</v>
       </c>
       <c r="B12" s="70">
         <v>7</v>
       </c>
       <c r="C12" s="70" t="s">
-        <v>112</v>
+        <v>104</v>
       </c>
       <c r="D12" s="70" t="s">
-        <v>113</v>
+        <v>105</v>
       </c>
       <c r="E12" s="70" t="s">
-        <v>114</v>
+        <v>106</v>
       </c>
       <c r="F12" s="80">
         <v>3.3</v>
       </c>
       <c r="G12" s="147">
-        <v>72600.7</v>
+        <v>87667.7</v>
       </c>
       <c r="H12" s="148">
-        <f>G12</f>
-        <v>72600.7</v>
+        <v>90297.7</v>
       </c>
       <c r="I12" s="83"/>
       <c r="J12" s="134">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>-2630</v>
       </c>
       <c r="K12" s="84">
         <f t="shared" si="1"/>
@@ -3297,23 +3329,23 @@
       </c>
       <c r="L12" s="85">
         <f t="shared" si="2"/>
-        <v>1562.0220000000002</v>
+        <v>5973</v>
       </c>
       <c r="M12" s="85">
         <f t="shared" si="3"/>
-        <v>86105.199840000001</v>
+        <v>99000</v>
       </c>
       <c r="N12" s="130">
         <f t="shared" si="4"/>
-        <v>87667.221839999998</v>
+        <v>102343</v>
       </c>
       <c r="O12" s="132" t="str">
         <f t="shared" si="5"/>
-        <v>$87667,7</v>
+        <v>$102343,7</v>
       </c>
       <c r="P12" s="136" t="str">
         <f t="shared" si="6"/>
-        <v>$90297,7</v>
+        <v>$105413,7</v>
       </c>
       <c r="Q12" s="51" t="str">
         <f t="shared" si="7"/>
@@ -3322,119 +3354,120 @@
     </row>
     <row r="13" spans="1:20" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="5" t="s">
-        <v>115</v>
+        <v>107</v>
       </c>
       <c r="B13" s="70">
         <v>23</v>
       </c>
       <c r="C13" s="70" t="s">
-        <v>116</v>
+        <v>108</v>
       </c>
       <c r="D13" s="70" t="s">
-        <v>117</v>
+        <v>109</v>
       </c>
       <c r="E13" s="70" t="s">
-        <v>118</v>
+        <v>110</v>
       </c>
       <c r="F13" s="80">
         <v>6.3</v>
       </c>
       <c r="G13" s="81">
-        <v>138600.23000000001</v>
+        <v>180595.23</v>
       </c>
       <c r="H13" s="82">
-        <v>126000</v>
+        <f>177613+2982.23</f>
+        <v>180595.23</v>
       </c>
       <c r="I13" s="83"/>
       <c r="J13" s="134">
         <f t="shared" si="0"/>
-        <v>12600.23000000001</v>
+        <v>0</v>
       </c>
       <c r="K13" s="84">
         <f t="shared" si="1"/>
-        <v>630.01150000000052</v>
+        <v>0</v>
       </c>
       <c r="L13" s="85">
         <f t="shared" si="2"/>
-        <v>2982.0419999999999</v>
+        <v>11403</v>
       </c>
       <c r="M13" s="85">
         <f t="shared" si="3"/>
-        <v>164382.65424</v>
+        <v>189000</v>
       </c>
       <c r="N13" s="130">
         <f t="shared" si="4"/>
-        <v>180594.93774000002</v>
+        <v>200403</v>
       </c>
       <c r="O13" s="132" t="str">
         <f t="shared" si="5"/>
-        <v>$180595,23</v>
+        <v>$200403,23</v>
       </c>
       <c r="P13" s="136" t="str">
         <f t="shared" si="6"/>
-        <v>$186013,23</v>
+        <v>$206415,23</v>
       </c>
       <c r="Q13" s="51" t="str">
         <f t="shared" si="7"/>
         <v>23</v>
       </c>
       <c r="S13" t="s">
-        <v>119</v>
+        <v>111</v>
       </c>
     </row>
     <row r="14" spans="1:20" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" s="5" t="s">
-        <v>115</v>
+        <v>107</v>
       </c>
       <c r="B14" s="70">
         <v>22</v>
       </c>
       <c r="C14" s="70" t="s">
-        <v>120</v>
+        <v>112</v>
       </c>
       <c r="D14" s="70" t="s">
-        <v>121</v>
+        <v>113</v>
       </c>
       <c r="E14" s="70" t="s">
-        <v>122</v>
+        <v>114</v>
       </c>
       <c r="F14" s="80">
         <v>5.0999999999999996</v>
       </c>
       <c r="G14" s="81">
-        <v>112200.22</v>
+        <v>135696.22</v>
       </c>
       <c r="H14" s="82">
-        <v>112000</v>
+        <v>135696.22</v>
       </c>
       <c r="I14" s="83"/>
       <c r="J14" s="134">
         <f t="shared" si="0"/>
-        <v>200.22000000000116</v>
+        <v>0</v>
       </c>
       <c r="K14" s="84">
         <f t="shared" si="1"/>
-        <v>10.01100000000006</v>
+        <v>0</v>
       </c>
       <c r="L14" s="85">
         <f t="shared" si="2"/>
-        <v>2414.0339999999997</v>
+        <v>9231</v>
       </c>
       <c r="M14" s="85">
         <f t="shared" si="3"/>
-        <v>133071.67247999998</v>
+        <v>153000</v>
       </c>
       <c r="N14" s="130">
         <f t="shared" si="4"/>
-        <v>135695.93747999999</v>
+        <v>162231</v>
       </c>
       <c r="O14" s="132" t="str">
         <f t="shared" si="5"/>
-        <v>$135696,22</v>
+        <v>$162231,22</v>
       </c>
       <c r="P14" s="136" t="str">
         <f t="shared" si="6"/>
-        <v>$139767,22</v>
+        <v>$167098,22</v>
       </c>
       <c r="Q14" s="51" t="str">
         <f t="shared" si="7"/>
@@ -3443,56 +3476,55 @@
     </row>
     <row r="15" spans="1:20" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" s="5" t="s">
-        <v>123</v>
+        <v>115</v>
       </c>
       <c r="B15" s="70">
         <v>21</v>
       </c>
       <c r="C15" s="70" t="s">
-        <v>124</v>
+        <v>116</v>
       </c>
       <c r="D15" s="70" t="s">
-        <v>125</v>
+        <v>117</v>
       </c>
       <c r="E15" s="71"/>
       <c r="F15" s="80">
         <v>8.1999999999999993</v>
       </c>
       <c r="G15" s="81">
-        <v>180400.21</v>
+        <v>217840.21</v>
       </c>
       <c r="H15" s="82">
-        <f>G15</f>
-        <v>180400.21</v>
+        <v>213958.21</v>
       </c>
       <c r="I15" s="83"/>
       <c r="J15" s="134">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>3882</v>
       </c>
       <c r="K15" s="84">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>194.10000000000002</v>
       </c>
       <c r="L15" s="85">
         <f t="shared" si="2"/>
-        <v>3881.3879999999995</v>
+        <v>14841.999999999998</v>
       </c>
       <c r="M15" s="85">
         <f t="shared" si="3"/>
-        <v>213958.37535999998</v>
+        <v>245999.99999999997</v>
       </c>
       <c r="N15" s="130">
         <f t="shared" si="4"/>
-        <v>217839.76335999998</v>
+        <v>264918.09999999998</v>
       </c>
       <c r="O15" s="132" t="str">
         <f t="shared" si="5"/>
-        <v>$217840,21</v>
+        <v>$264918,21</v>
       </c>
       <c r="P15" s="136" t="str">
         <f t="shared" si="6"/>
-        <v>$224375,21</v>
+        <v>$272866,21</v>
       </c>
       <c r="Q15" s="51" t="str">
         <f t="shared" si="7"/>
@@ -3501,29 +3533,29 @@
     </row>
     <row r="16" spans="1:20" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A16" s="5" t="s">
-        <v>123</v>
+        <v>115</v>
       </c>
       <c r="B16" s="70">
         <v>14</v>
       </c>
       <c r="C16" s="70" t="s">
-        <v>126</v>
+        <v>118</v>
       </c>
       <c r="D16" s="70" t="s">
-        <v>127</v>
+        <v>119</v>
       </c>
       <c r="E16" s="70" t="s">
-        <v>128</v>
+        <v>120</v>
       </c>
       <c r="F16" s="80">
         <v>6.1</v>
       </c>
       <c r="G16" s="81">
-        <v>134200.14000000001</v>
+        <v>162052.14000000001</v>
       </c>
       <c r="H16" s="82">
         <f>G16</f>
-        <v>134200.14000000001</v>
+        <v>162052.14000000001</v>
       </c>
       <c r="I16" s="83"/>
       <c r="J16" s="134">
@@ -3536,23 +3568,23 @@
       </c>
       <c r="L16" s="85">
         <f t="shared" si="2"/>
-        <v>2887.3739999999998</v>
+        <v>11041</v>
       </c>
       <c r="M16" s="85">
         <f t="shared" si="3"/>
-        <v>159164.15727999998</v>
+        <v>183000</v>
       </c>
       <c r="N16" s="130">
         <f t="shared" si="4"/>
-        <v>162051.53128</v>
+        <v>194041</v>
       </c>
       <c r="O16" s="132" t="str">
         <f t="shared" si="5"/>
-        <v>$162052,14</v>
+        <v>$194041,14</v>
       </c>
       <c r="P16" s="136" t="str">
         <f t="shared" si="6"/>
-        <v>$166913,14</v>
+        <v>$199862,14</v>
       </c>
       <c r="Q16" s="51" t="str">
         <f t="shared" si="7"/>
@@ -3561,32 +3593,31 @@
     </row>
     <row r="17" spans="1:20" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A17" s="5" t="s">
-        <v>129</v>
+        <v>121</v>
       </c>
       <c r="B17" s="70">
         <v>13</v>
       </c>
       <c r="C17" s="70" t="s">
-        <v>130</v>
+        <v>122</v>
       </c>
       <c r="D17" s="70" t="s">
-        <v>131</v>
+        <v>123</v>
       </c>
       <c r="E17" s="71"/>
       <c r="F17" s="80">
         <v>5</v>
       </c>
       <c r="G17" s="81">
-        <v>110000.13</v>
+        <v>132829.13</v>
       </c>
       <c r="H17" s="82">
-        <f>G17</f>
-        <v>110000.13</v>
+        <v>136814.13</v>
       </c>
       <c r="I17" s="83"/>
       <c r="J17" s="134">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>-3985</v>
       </c>
       <c r="K17" s="84">
         <f t="shared" si="1"/>
@@ -3594,23 +3625,23 @@
       </c>
       <c r="L17" s="85">
         <f t="shared" si="2"/>
-        <v>2366.7000000000003</v>
+        <v>9050</v>
       </c>
       <c r="M17" s="85">
         <f t="shared" si="3"/>
-        <v>130462.424</v>
+        <v>150000</v>
       </c>
       <c r="N17" s="130">
         <f t="shared" si="4"/>
-        <v>132829.12400000001</v>
+        <v>155065</v>
       </c>
       <c r="O17" s="132" t="str">
         <f t="shared" si="5"/>
-        <v>$132829,13</v>
+        <v>$155065,13</v>
       </c>
       <c r="P17" s="136" t="str">
         <f t="shared" si="6"/>
-        <v>$136814,13</v>
+        <v>$159717,13</v>
       </c>
       <c r="Q17" s="51" t="str">
         <f t="shared" si="7"/>
@@ -3619,57 +3650,57 @@
     </row>
     <row r="18" spans="1:20" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A18" s="5" t="s">
-        <v>129</v>
+        <v>121</v>
       </c>
       <c r="B18" s="70">
         <v>12</v>
       </c>
       <c r="C18" s="70" t="s">
-        <v>132</v>
+        <v>124</v>
       </c>
       <c r="D18" s="70" t="s">
-        <v>133</v>
+        <v>125</v>
       </c>
       <c r="E18" s="70" t="s">
-        <v>134</v>
+        <v>126</v>
       </c>
       <c r="F18" s="80">
         <v>8.1999999999999993</v>
       </c>
       <c r="G18" s="81">
-        <v>12969592.119999999</v>
+        <v>13646491.119999999</v>
       </c>
       <c r="H18" s="82">
-        <v>180400</v>
+        <v>217839</v>
       </c>
       <c r="I18" s="83"/>
       <c r="J18" s="134">
         <f t="shared" si="0"/>
-        <v>12789192.119999999</v>
+        <v>13428652.119999999</v>
       </c>
       <c r="K18" s="84">
         <f t="shared" si="1"/>
-        <v>639459.60600000003</v>
+        <v>671432.60600000003</v>
       </c>
       <c r="L18" s="85">
         <f t="shared" si="2"/>
-        <v>3881.3879999999995</v>
+        <v>14841.999999999998</v>
       </c>
       <c r="M18" s="85">
         <f t="shared" si="3"/>
-        <v>213958.37535999998</v>
+        <v>245999.99999999997</v>
       </c>
       <c r="N18" s="130">
         <f t="shared" si="4"/>
-        <v>13646491.489360001</v>
+        <v>14360926.726</v>
       </c>
       <c r="O18" s="132" t="str">
         <f t="shared" si="5"/>
-        <v>$13646491,12</v>
+        <v>$14360927,12</v>
       </c>
       <c r="P18" s="136" t="str">
         <f t="shared" si="6"/>
-        <v>$14055886,12</v>
+        <v>$14791755,12</v>
       </c>
       <c r="Q18" s="51" t="str">
         <f t="shared" si="7"/>
@@ -3678,53 +3709,53 @@
     </row>
     <row r="19" spans="1:20" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A19" s="5" t="s">
-        <v>135</v>
+        <v>127</v>
       </c>
       <c r="B19" s="70">
         <v>17</v>
       </c>
       <c r="C19" s="70" t="s">
-        <v>136</v>
+        <v>128</v>
       </c>
       <c r="D19" s="70" t="s">
-        <v>133</v>
+        <v>125</v>
       </c>
       <c r="E19" s="71"/>
       <c r="F19" s="80">
         <v>6.1</v>
       </c>
       <c r="G19" s="81">
-        <v>8915960.1699999999</v>
+        <v>9523810.1699999999</v>
       </c>
       <c r="H19" s="82"/>
       <c r="I19" s="83"/>
       <c r="J19" s="134">
         <f t="shared" si="0"/>
-        <v>8915960.1699999999</v>
+        <v>9523810.1699999999</v>
       </c>
       <c r="K19" s="84">
         <f t="shared" si="1"/>
-        <v>445798.0085</v>
+        <v>476190.5085</v>
       </c>
       <c r="L19" s="85">
         <f t="shared" si="2"/>
-        <v>2887.3739999999998</v>
+        <v>11041</v>
       </c>
       <c r="M19" s="85">
         <f t="shared" si="3"/>
-        <v>159164.15727999998</v>
+        <v>183000</v>
       </c>
       <c r="N19" s="130">
         <f t="shared" si="4"/>
-        <v>9523809.7097800002</v>
+        <v>10194041.6785</v>
       </c>
       <c r="O19" s="132" t="str">
         <f t="shared" si="5"/>
-        <v>$9523810,17</v>
+        <v>$10194042,17</v>
       </c>
       <c r="P19" s="136" t="str">
         <f t="shared" si="6"/>
-        <v>$9809524,17</v>
+        <v>$10499863,17</v>
       </c>
       <c r="Q19" s="51" t="str">
         <f t="shared" si="7"/>
@@ -3733,115 +3764,118 @@
     </row>
     <row r="20" spans="1:20" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A20" s="5" t="s">
-        <v>135</v>
+        <v>127</v>
       </c>
       <c r="B20" s="70">
         <v>16</v>
       </c>
       <c r="C20" s="70" t="s">
-        <v>137</v>
+        <v>129</v>
       </c>
       <c r="D20" s="70" t="s">
-        <v>138</v>
+        <v>130</v>
       </c>
       <c r="E20" s="71" t="s">
-        <v>139</v>
+        <v>131</v>
       </c>
       <c r="F20" s="80">
         <v>5</v>
       </c>
       <c r="G20" s="81">
-        <v>110000.16</v>
+        <v>132829.16</v>
       </c>
       <c r="H20" s="82">
-        <v>110000</v>
+        <f>118000+5000+1000</f>
+        <v>124000</v>
       </c>
       <c r="I20" s="83"/>
       <c r="J20" s="134">
         <f t="shared" si="0"/>
-        <v>0.16000000000349246</v>
+        <v>8829.1600000000035</v>
       </c>
       <c r="K20" s="84">
         <f t="shared" si="1"/>
-        <v>8.0000000001746226E-3</v>
+        <v>441.4580000000002</v>
       </c>
       <c r="L20" s="85">
         <f t="shared" si="2"/>
-        <v>2366.7000000000003</v>
+        <v>9050</v>
       </c>
       <c r="M20" s="85">
         <f t="shared" si="3"/>
-        <v>130462.424</v>
+        <v>150000</v>
       </c>
       <c r="N20" s="130">
         <f t="shared" si="4"/>
-        <v>132829.29200000002</v>
+        <v>168320.61800000002</v>
       </c>
       <c r="O20" s="132" t="str">
         <f t="shared" si="5"/>
-        <v>$132829,16</v>
+        <v>$168321,16</v>
       </c>
       <c r="P20" s="136" t="str">
         <f t="shared" si="6"/>
-        <v>$136814,16</v>
+        <v>$173370,16</v>
       </c>
       <c r="Q20" s="51" t="str">
         <f t="shared" si="7"/>
         <v>16</v>
       </c>
+      <c r="S20" t="s">
+        <v>164</v>
+      </c>
     </row>
     <row r="21" spans="1:20" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A21" s="5" t="s">
-        <v>140</v>
+        <v>132</v>
       </c>
       <c r="B21" s="70">
         <v>15</v>
       </c>
       <c r="C21" s="70" t="s">
-        <v>141</v>
+        <v>133</v>
       </c>
       <c r="D21" s="70" t="s">
-        <v>142</v>
+        <v>134</v>
       </c>
       <c r="E21" s="70"/>
       <c r="F21" s="80">
         <v>8.1999999999999993</v>
       </c>
       <c r="G21" s="81">
-        <v>180400.15</v>
+        <v>217840.15</v>
       </c>
       <c r="H21" s="82">
-        <f>G21</f>
-        <v>180400.15</v>
+        <v>213958.15</v>
       </c>
       <c r="I21" s="83"/>
       <c r="J21" s="134">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>3882</v>
       </c>
       <c r="K21" s="84">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>194.10000000000002</v>
       </c>
       <c r="L21" s="85">
         <f t="shared" si="2"/>
-        <v>3881.3879999999995</v>
+        <v>14841.999999999998</v>
       </c>
       <c r="M21" s="85">
         <f t="shared" si="3"/>
-        <v>213958.37535999998</v>
+        <v>245999.99999999997</v>
       </c>
       <c r="N21" s="130">
         <f t="shared" si="4"/>
-        <v>217839.76335999998</v>
+        <v>264918.09999999998</v>
       </c>
       <c r="O21" s="132" t="str">
         <f t="shared" si="5"/>
-        <v>$217840,15</v>
+        <v>$264918,15</v>
       </c>
       <c r="P21" s="136" t="str">
         <f t="shared" si="6"/>
-        <v>$224375,15</v>
+        <v>$272866,15</v>
       </c>
       <c r="Q21" s="51" t="str">
         <f t="shared" si="7"/>
@@ -3851,27 +3885,27 @@
     </row>
     <row r="22" spans="1:20" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A22" s="5" t="s">
-        <v>140</v>
+        <v>132</v>
       </c>
       <c r="B22" s="70">
         <v>20</v>
       </c>
       <c r="C22" s="70" t="s">
-        <v>143</v>
+        <v>135</v>
       </c>
       <c r="D22" s="70" t="s">
-        <v>144</v>
+        <v>136</v>
       </c>
       <c r="E22" s="71"/>
       <c r="F22" s="80">
         <v>6.1</v>
       </c>
       <c r="G22" s="82">
-        <v>134200.20000000001</v>
+        <v>162052.20000000001</v>
       </c>
       <c r="H22" s="82">
         <f>G22</f>
-        <v>134200.20000000001</v>
+        <v>162052.20000000001</v>
       </c>
       <c r="I22" s="83"/>
       <c r="J22" s="84">
@@ -3884,55 +3918,55 @@
       </c>
       <c r="L22" s="85">
         <f t="shared" si="2"/>
-        <v>2887.3739999999998</v>
+        <v>11041</v>
       </c>
       <c r="M22" s="85">
         <f t="shared" si="3"/>
-        <v>159164.15727999998</v>
+        <v>183000</v>
       </c>
       <c r="N22" s="130">
         <f t="shared" si="4"/>
-        <v>162051.53128</v>
+        <v>194041</v>
       </c>
       <c r="O22" s="132" t="str">
         <f t="shared" si="5"/>
-        <v>$162052,20</v>
+        <v>$194041,20</v>
       </c>
       <c r="P22" s="136" t="str">
         <f t="shared" si="6"/>
-        <v>$166913,20</v>
+        <v>$199862,20</v>
       </c>
       <c r="Q22" s="51" t="str">
         <f t="shared" si="7"/>
         <v>20</v>
       </c>
       <c r="T22" t="s">
-        <v>145</v>
+        <v>137</v>
       </c>
     </row>
     <row r="23" spans="1:20" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A23" s="5" t="s">
-        <v>146</v>
+        <v>138</v>
       </c>
       <c r="B23" s="70">
         <v>19</v>
       </c>
       <c r="C23" s="70" t="s">
-        <v>147</v>
+        <v>139</v>
       </c>
       <c r="D23" s="70" t="s">
-        <v>148</v>
+        <v>140</v>
       </c>
       <c r="E23" s="70"/>
       <c r="F23" s="80">
         <v>5</v>
       </c>
       <c r="G23" s="81">
-        <v>110000.19</v>
+        <v>132829.19</v>
       </c>
       <c r="H23" s="82">
         <f>G23</f>
-        <v>110000.19</v>
+        <v>132829.19</v>
       </c>
       <c r="I23" s="83"/>
       <c r="J23" s="84">
@@ -3945,23 +3979,23 @@
       </c>
       <c r="L23" s="85">
         <f t="shared" si="2"/>
-        <v>2366.7000000000003</v>
+        <v>9050</v>
       </c>
       <c r="M23" s="85">
         <f t="shared" si="3"/>
-        <v>130462.424</v>
+        <v>150000</v>
       </c>
       <c r="N23" s="130">
         <f t="shared" si="4"/>
-        <v>132829.12400000001</v>
+        <v>159050</v>
       </c>
       <c r="O23" s="132" t="str">
         <f t="shared" si="5"/>
-        <v>$132829,19</v>
+        <v>$159050,19</v>
       </c>
       <c r="P23" s="136" t="str">
         <f t="shared" si="6"/>
-        <v>$136814,19</v>
+        <v>$163822,19</v>
       </c>
       <c r="Q23" s="51" t="str">
         <f t="shared" si="7"/>
@@ -3970,27 +4004,27 @@
     </row>
     <row r="24" spans="1:20" ht="17.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A24" s="5" t="s">
-        <v>146</v>
+        <v>138</v>
       </c>
       <c r="B24" s="70">
         <v>18</v>
       </c>
       <c r="C24" s="70" t="s">
-        <v>149</v>
+        <v>141</v>
       </c>
       <c r="D24" s="70" t="s">
-        <v>150</v>
+        <v>142</v>
       </c>
       <c r="E24" s="71"/>
       <c r="F24" s="80">
         <v>8.1999999999999993</v>
       </c>
       <c r="G24" s="81">
-        <v>175480.18</v>
+        <v>217840.18</v>
       </c>
       <c r="H24" s="82">
         <f>G24</f>
-        <v>175480.18</v>
+        <v>217840.18</v>
       </c>
       <c r="I24" s="83"/>
       <c r="J24" s="84">
@@ -4003,30 +4037,30 @@
       </c>
       <c r="L24" s="85">
         <f t="shared" si="2"/>
-        <v>3881.3879999999995</v>
+        <v>14841.999999999998</v>
       </c>
       <c r="M24" s="85">
         <f t="shared" si="3"/>
-        <v>213958.37535999998</v>
+        <v>245999.99999999997</v>
       </c>
       <c r="N24" s="130">
         <f t="shared" si="4"/>
-        <v>217839.76335999998</v>
+        <v>260841.99999999997</v>
       </c>
       <c r="O24" s="132" t="str">
         <f t="shared" si="5"/>
-        <v>$217840,18</v>
+        <v>$260842,18</v>
       </c>
       <c r="P24" s="136" t="str">
         <f t="shared" si="6"/>
-        <v>$224375,18</v>
+        <v>$268667,18</v>
       </c>
       <c r="Q24" s="51" t="str">
         <f t="shared" si="7"/>
         <v>18</v>
       </c>
       <c r="T24" t="s">
-        <v>151</v>
+        <v>143</v>
       </c>
     </row>
     <row r="25" spans="1:20" ht="17.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
@@ -4040,11 +4074,11 @@
       </c>
       <c r="G25" s="62">
         <f t="shared" si="8"/>
-        <v>23902986.899999999</v>
+        <v>25754326.899999999</v>
       </c>
       <c r="H25" s="68">
         <f t="shared" si="8"/>
-        <v>1915682.4999999998</v>
+        <v>2639132.91</v>
       </c>
       <c r="I25" s="62">
         <f t="shared" si="8"/>
@@ -4052,19 +4086,19 @@
       </c>
       <c r="J25" s="68">
         <f t="shared" si="8"/>
-        <v>21987304.399999999</v>
+        <v>23115193.989999998</v>
       </c>
       <c r="K25" s="68">
         <f t="shared" si="8"/>
-        <v>1099565.19</v>
+        <v>1156241.8905000002</v>
       </c>
       <c r="L25" s="68">
         <f t="shared" si="8"/>
-        <v>47333.999999999993</v>
+        <v>181000</v>
       </c>
       <c r="M25" s="68">
         <f t="shared" si="8"/>
-        <v>2609248.4799999995</v>
+        <v>3000000</v>
       </c>
       <c r="N25" s="131"/>
       <c r="O25" s="90">
@@ -4082,8 +4116,8 @@
     </row>
     <row r="27" spans="1:20" hidden="1" x14ac:dyDescent="0.25"/>
     <row r="28" spans="1:20" ht="9" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="D28" s="158" t="s">
-        <v>152</v>
+      <c r="D28" s="161" t="s">
+        <v>144</v>
       </c>
       <c r="E28" s="151"/>
       <c r="F28" s="151"/>
@@ -4169,13 +4203,6 @@
     </row>
   </sheetData>
   <mergeCells count="19">
-    <mergeCell ref="D28:O33"/>
-    <mergeCell ref="C4:C5"/>
-    <mergeCell ref="E4:E5"/>
-    <mergeCell ref="F1:O1"/>
-    <mergeCell ref="D4:D5"/>
-    <mergeCell ref="J4:J5"/>
-    <mergeCell ref="L4:L5"/>
     <mergeCell ref="A4:A5"/>
     <mergeCell ref="G4:G5"/>
     <mergeCell ref="I4:I5"/>
@@ -4188,8 +4215,15 @@
     <mergeCell ref="N4:N5"/>
     <mergeCell ref="P4:P5"/>
     <mergeCell ref="O3:P3"/>
+    <mergeCell ref="D28:O33"/>
+    <mergeCell ref="C4:C5"/>
+    <mergeCell ref="E4:E5"/>
+    <mergeCell ref="F1:O1"/>
+    <mergeCell ref="D4:D5"/>
+    <mergeCell ref="J4:J5"/>
+    <mergeCell ref="L4:L5"/>
   </mergeCells>
   <pageMargins left="0.25" right="0.25" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="landscape"/>
+  <pageSetup paperSize="9" orientation="landscape" r:id="rId1"/>
 </worksheet>
 </file>
--- a/PUEYRREDON 1494/Junio/PUEYRREDON JUNIO.xlsx
+++ b/PUEYRREDON 1494/Junio/PUEYRREDON JUNIO.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28827"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28925"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\OneDrive\Desktop\RC CONSORCIO 2025\PUEYRREDON 1494\Junio\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7FA0B8FE-EC7D-427E-BF08-DC4449B83F75}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{727C1377-427C-4D1F-B5C0-18B587D2FCCE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" tabRatio="793" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="183" uniqueCount="165">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="184" uniqueCount="166">
   <si>
     <t>MAIL: consorciopueyrredon1494@gmail.com</t>
   </si>
@@ -520,6 +520,9 @@
   </si>
   <si>
     <t>DEPOSITA SIEMPRE VALERIA</t>
+  </si>
+  <si>
+    <t>el mes pasado valeria hizo tres depositos (uno de 118mil, otro de 5mil y un ultimo de 10mil) de los cuales nosotros si bien se los pusimos, le escribimos mal el ultimo, en lugar de haberle puesto que hizo un deposito de 118mil, de 5mil y de 10 mil le pusimos de 118mil de 5mil y de mil, por lo que no debe tener deuda alguna, es mas, el mes anterior si le hubiesemos imputado bien los pagos le hubiesen quedado 171 pesos a favor)</t>
   </si>
 </sst>
 </file>
@@ -734,7 +737,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="12">
+  <fills count="13">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -801,6 +804,12 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="-0.249977111117893"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="30">
     <border>
@@ -1164,7 +1173,7 @@
     <xf numFmtId="165" fontId="1" fillId="0" borderId="0"/>
     <xf numFmtId="43" fontId="1" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="183">
+  <cellXfs count="184">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="16" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -1367,26 +1376,19 @@
     <xf numFmtId="0" fontId="23" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="25" fillId="11" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="166" fontId="4" fillId="2" borderId="6" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="9" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="9" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="18" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="9" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="27" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="22" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="28" xfId="0" applyBorder="1"/>
@@ -1400,26 +1402,26 @@
     <xf numFmtId="0" fontId="23" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="19" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="18" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="19" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="13" fillId="3" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="19" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="13" fillId="3" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="20" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="3" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="3" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="18" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="13" fillId="3" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -1437,9 +1439,17 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1"/>
-    <xf numFmtId="164" fontId="25" fillId="11" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
-    <xf numFmtId="166" fontId="4" fillId="2" borderId="6" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="3" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="3" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="166" fontId="21" fillId="12" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="12" borderId="0" xfId="0" applyFill="1"/>
   </cellXfs>
   <cellStyles count="4">
     <cellStyle name="Millares" xfId="3" builtinId="3"/>
@@ -1831,49 +1841,49 @@
       <c r="E7" s="21"/>
     </row>
     <row r="9" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="B9" s="150" t="s">
+      <c r="B9" s="164" t="s">
         <v>9</v>
       </c>
-      <c r="C9" s="151"/>
+      <c r="C9" s="153"/>
     </row>
     <row r="10" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="B10" s="151"/>
-      <c r="C10" s="151"/>
+      <c r="B10" s="153"/>
+      <c r="C10" s="153"/>
     </row>
     <row r="11" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="B11" s="151"/>
-      <c r="C11" s="151"/>
+      <c r="B11" s="153"/>
+      <c r="C11" s="153"/>
     </row>
     <row r="13" spans="1:5" hidden="1" x14ac:dyDescent="0.25"/>
     <row r="14" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A14" s="154" t="s">
+      <c r="A14" s="165" t="s">
         <v>10</v>
       </c>
-      <c r="B14" s="151"/>
-      <c r="C14" s="151"/>
-      <c r="D14" s="151"/>
-      <c r="E14" s="151"/>
+      <c r="B14" s="153"/>
+      <c r="C14" s="153"/>
+      <c r="D14" s="153"/>
+      <c r="E14" s="153"/>
     </row>
     <row r="15" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A15" s="151"/>
-      <c r="B15" s="151"/>
-      <c r="C15" s="151"/>
-      <c r="D15" s="151"/>
-      <c r="E15" s="151"/>
+      <c r="A15" s="153"/>
+      <c r="B15" s="153"/>
+      <c r="C15" s="153"/>
+      <c r="D15" s="153"/>
+      <c r="E15" s="153"/>
     </row>
     <row r="16" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A16" s="151"/>
-      <c r="B16" s="151"/>
-      <c r="C16" s="151"/>
-      <c r="D16" s="151"/>
-      <c r="E16" s="151"/>
+      <c r="A16" s="153"/>
+      <c r="B16" s="153"/>
+      <c r="C16" s="153"/>
+      <c r="D16" s="153"/>
+      <c r="E16" s="153"/>
     </row>
     <row r="17" spans="1:8" ht="53.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A17" s="151"/>
-      <c r="B17" s="151"/>
-      <c r="C17" s="151"/>
-      <c r="D17" s="151"/>
-      <c r="E17" s="151"/>
+      <c r="A17" s="153"/>
+      <c r="B17" s="153"/>
+      <c r="C17" s="153"/>
+      <c r="D17" s="153"/>
+      <c r="E17" s="153"/>
     </row>
     <row r="18" spans="1:8" ht="14.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="19" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
@@ -1983,12 +1993,11 @@
       </c>
       <c r="B30" s="65"/>
       <c r="C30" s="65"/>
-      <c r="D30" s="180">
+      <c r="D30" s="150">
         <f>SUM(D28:D29)</f>
         <v>310989</v>
       </c>
       <c r="E30" s="97"/>
-      <c r="H30" s="181"/>
     </row>
     <row r="31" spans="1:8" ht="14.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A31" s="30" t="s">
@@ -2060,10 +2069,10 @@
       <c r="E36" s="74"/>
     </row>
     <row r="37" spans="1:7" s="44" customFormat="1" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A37" s="155" t="s">
+      <c r="A37" s="166" t="s">
         <v>24</v>
       </c>
-      <c r="B37" s="153"/>
+      <c r="B37" s="156"/>
       <c r="C37" s="63"/>
       <c r="D37" s="143">
         <v>87562.7</v>
@@ -2071,10 +2080,10 @@
       <c r="E37" s="122"/>
     </row>
     <row r="38" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A38" s="155" t="s">
+      <c r="A38" s="166" t="s">
         <v>25</v>
       </c>
-      <c r="B38" s="153"/>
+      <c r="B38" s="156"/>
       <c r="C38" s="63"/>
       <c r="D38" s="144">
         <v>6646.91</v>
@@ -2254,12 +2263,12 @@
       </c>
     </row>
     <row r="52" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A52" s="152" t="s">
+      <c r="A52" s="155" t="s">
         <v>149</v>
       </c>
-      <c r="B52" s="153"/>
+      <c r="B52" s="156"/>
       <c r="C52" s="64"/>
-      <c r="D52" s="182">
+      <c r="D52" s="151">
         <v>54750</v>
       </c>
       <c r="E52" s="124" t="s">
@@ -2404,26 +2413,26 @@
       <c r="E67" s="119"/>
     </row>
     <row r="68" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A68" s="152" t="s">
+      <c r="A68" s="155" t="s">
         <v>163</v>
       </c>
-      <c r="B68" s="158"/>
+      <c r="B68" s="157"/>
       <c r="C68" s="5"/>
-      <c r="D68" s="162">
+      <c r="D68" s="161">
         <v>181000</v>
       </c>
-      <c r="E68" s="164"/>
+      <c r="E68" s="163"/>
     </row>
     <row r="69" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A69" s="159"/>
-      <c r="B69" s="160"/>
+      <c r="A69" s="158"/>
+      <c r="B69" s="159"/>
       <c r="C69" s="61"/>
-      <c r="D69" s="163"/>
-      <c r="E69" s="163"/>
+      <c r="D69" s="162"/>
+      <c r="E69" s="162"/>
     </row>
     <row r="70" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A70" s="152"/>
-      <c r="B70" s="153"/>
+      <c r="A70" s="155"/>
+      <c r="B70" s="156"/>
       <c r="C70" s="61"/>
       <c r="D70" s="42"/>
       <c r="E70" s="149"/>
@@ -2501,25 +2510,25 @@
     <row r="81" spans="1:5" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="82" spans="1:5" hidden="1" x14ac:dyDescent="0.25"/>
     <row r="83" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A83" s="156"/>
-      <c r="B83" s="151"/>
-      <c r="C83" s="151"/>
-      <c r="D83" s="151"/>
-      <c r="E83" s="151"/>
+      <c r="A83" s="152"/>
+      <c r="B83" s="153"/>
+      <c r="C83" s="153"/>
+      <c r="D83" s="153"/>
+      <c r="E83" s="153"/>
     </row>
     <row r="84" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A84" s="151"/>
-      <c r="B84" s="151"/>
-      <c r="C84" s="151"/>
-      <c r="D84" s="151"/>
-      <c r="E84" s="151"/>
+      <c r="A84" s="153"/>
+      <c r="B84" s="153"/>
+      <c r="C84" s="153"/>
+      <c r="D84" s="153"/>
+      <c r="E84" s="153"/>
     </row>
     <row r="85" spans="1:5" ht="38.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A85" s="151"/>
-      <c r="B85" s="151"/>
-      <c r="C85" s="151"/>
-      <c r="D85" s="151"/>
-      <c r="E85" s="151"/>
+      <c r="A85" s="153"/>
+      <c r="B85" s="153"/>
+      <c r="C85" s="153"/>
+      <c r="D85" s="153"/>
+      <c r="E85" s="153"/>
     </row>
     <row r="87" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A87" s="23" t="s">
@@ -2672,16 +2681,16 @@
     <row r="105" spans="1:13" hidden="1" x14ac:dyDescent="0.25"/>
     <row r="106" spans="1:13" ht="60.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="107" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A107" s="157" t="s">
+      <c r="A107" s="154" t="s">
         <v>61</v>
       </c>
-      <c r="B107" s="151"/>
-      <c r="C107" s="151"/>
+      <c r="B107" s="153"/>
+      <c r="C107" s="153"/>
     </row>
     <row r="108" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A108" s="151"/>
-      <c r="B108" s="151"/>
-      <c r="C108" s="151"/>
+      <c r="A108" s="153"/>
+      <c r="B108" s="153"/>
+      <c r="C108" s="153"/>
     </row>
     <row r="109" spans="1:13" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A109" s="63"/>
@@ -2709,35 +2718,40 @@
       <c r="M112" s="8"/>
     </row>
     <row r="113" spans="1:5" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A113" s="161"/>
-      <c r="B113" s="151"/>
-      <c r="C113" s="151"/>
-      <c r="D113" s="151"/>
-      <c r="E113" s="151"/>
+      <c r="A113" s="160"/>
+      <c r="B113" s="153"/>
+      <c r="C113" s="153"/>
+      <c r="D113" s="153"/>
+      <c r="E113" s="153"/>
     </row>
     <row r="114" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A114" s="151"/>
-      <c r="B114" s="151"/>
-      <c r="C114" s="151"/>
-      <c r="D114" s="151"/>
-      <c r="E114" s="151"/>
+      <c r="A114" s="153"/>
+      <c r="B114" s="153"/>
+      <c r="C114" s="153"/>
+      <c r="D114" s="153"/>
+      <c r="E114" s="153"/>
     </row>
     <row r="115" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A115" s="151"/>
-      <c r="B115" s="151"/>
-      <c r="C115" s="151"/>
-      <c r="D115" s="151"/>
-      <c r="E115" s="151"/>
+      <c r="A115" s="153"/>
+      <c r="B115" s="153"/>
+      <c r="C115" s="153"/>
+      <c r="D115" s="153"/>
+      <c r="E115" s="153"/>
     </row>
     <row r="116" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A116" s="151"/>
-      <c r="B116" s="151"/>
-      <c r="C116" s="151"/>
-      <c r="D116" s="151"/>
-      <c r="E116" s="151"/>
+      <c r="A116" s="153"/>
+      <c r="B116" s="153"/>
+      <c r="C116" s="153"/>
+      <c r="D116" s="153"/>
+      <c r="E116" s="153"/>
     </row>
   </sheetData>
   <mergeCells count="12">
+    <mergeCell ref="B9:C11"/>
+    <mergeCell ref="A52:B52"/>
+    <mergeCell ref="A14:E17"/>
+    <mergeCell ref="A37:B37"/>
+    <mergeCell ref="A38:B38"/>
     <mergeCell ref="A83:E85"/>
     <mergeCell ref="A107:C108"/>
     <mergeCell ref="A70:B70"/>
@@ -2745,11 +2759,6 @@
     <mergeCell ref="A113:E116"/>
     <mergeCell ref="D68:D69"/>
     <mergeCell ref="E68:E69"/>
-    <mergeCell ref="B9:C11"/>
-    <mergeCell ref="A52:B52"/>
-    <mergeCell ref="A14:E17"/>
-    <mergeCell ref="A37:B37"/>
-    <mergeCell ref="A38:B38"/>
   </mergeCells>
   <pageMargins left="0.25" right="0.25" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
@@ -2758,7 +2767,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A1:T33"/>
+  <dimension ref="A1:U33"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="5" hidden="1" customWidth="1"/>
@@ -2790,18 +2799,18 @@
         <v>62</v>
       </c>
       <c r="E1" s="6"/>
-      <c r="F1" s="169" t="s">
+      <c r="F1" s="179" t="s">
         <v>63</v>
       </c>
-      <c r="G1" s="151"/>
-      <c r="H1" s="151"/>
-      <c r="I1" s="151"/>
-      <c r="J1" s="151"/>
-      <c r="K1" s="151"/>
-      <c r="L1" s="151"/>
-      <c r="M1" s="151"/>
-      <c r="N1" s="151"/>
-      <c r="O1" s="151"/>
+      <c r="G1" s="153"/>
+      <c r="H1" s="153"/>
+      <c r="I1" s="153"/>
+      <c r="J1" s="153"/>
+      <c r="K1" s="153"/>
+      <c r="L1" s="153"/>
+      <c r="M1" s="153"/>
+      <c r="N1" s="153"/>
+      <c r="O1" s="153"/>
       <c r="P1" s="6"/>
     </row>
     <row r="2" spans="1:20" ht="12.95" customHeight="1" x14ac:dyDescent="0.25">
@@ -2824,11 +2833,11 @@
       </c>
       <c r="M2" s="6"/>
       <c r="N2" s="6"/>
-      <c r="O2" s="174">
+      <c r="O2" s="173">
         <f>T4</f>
         <v>3000000</v>
       </c>
-      <c r="P2" s="151"/>
+      <c r="P2" s="153"/>
       <c r="Q2" s="22"/>
     </row>
     <row r="3" spans="1:20" ht="12.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
@@ -2850,59 +2859,59 @@
       </c>
       <c r="M3" s="6"/>
       <c r="N3" s="6"/>
-      <c r="O3" s="178">
+      <c r="O3" s="177">
         <f>S6</f>
         <v>181000</v>
       </c>
-      <c r="P3" s="179"/>
+      <c r="P3" s="178"/>
     </row>
     <row r="4" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="A4" s="172" t="s">
+      <c r="A4" s="167" t="s">
         <v>67</v>
       </c>
-      <c r="B4" s="175" t="s">
+      <c r="B4" s="174" t="s">
         <v>68</v>
       </c>
-      <c r="C4" s="165" t="s">
+      <c r="C4" s="169" t="s">
         <v>69</v>
       </c>
-      <c r="D4" s="165" t="s">
+      <c r="D4" s="169" t="s">
         <v>70</v>
       </c>
-      <c r="E4" s="167" t="s">
+      <c r="E4" s="170" t="s">
         <v>71</v>
       </c>
-      <c r="F4" s="165" t="s">
+      <c r="F4" s="169" t="s">
         <v>72</v>
       </c>
-      <c r="G4" s="165" t="s">
+      <c r="G4" s="169" t="s">
         <v>73</v>
       </c>
-      <c r="H4" s="165" t="s">
+      <c r="H4" s="169" t="s">
         <v>74</v>
       </c>
-      <c r="I4" s="167" t="s">
+      <c r="I4" s="170" t="s">
         <v>75</v>
       </c>
-      <c r="J4" s="170" t="s">
+      <c r="J4" s="180" t="s">
         <v>76</v>
       </c>
-      <c r="K4" s="173" t="s">
+      <c r="K4" s="172" t="s">
         <v>77</v>
       </c>
-      <c r="L4" s="171" t="s">
+      <c r="L4" s="181" t="s">
         <v>78</v>
       </c>
-      <c r="M4" s="173" t="s">
+      <c r="M4" s="172" t="s">
         <v>79</v>
       </c>
-      <c r="N4" s="173" t="s">
+      <c r="N4" s="172" t="s">
         <v>80</v>
       </c>
       <c r="O4" s="69" t="s">
         <v>81</v>
       </c>
-      <c r="P4" s="177" t="s">
+      <c r="P4" s="176" t="s">
         <v>82</v>
       </c>
       <c r="S4" s="51"/>
@@ -2911,25 +2920,25 @@
       </c>
     </row>
     <row r="5" spans="1:20" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="166"/>
-      <c r="B5" s="176"/>
-      <c r="C5" s="166"/>
-      <c r="D5" s="166"/>
-      <c r="E5" s="168"/>
-      <c r="F5" s="166"/>
-      <c r="G5" s="166"/>
-      <c r="H5" s="166"/>
-      <c r="I5" s="168"/>
-      <c r="J5" s="168"/>
-      <c r="K5" s="168"/>
-      <c r="L5" s="166"/>
-      <c r="M5" s="168"/>
-      <c r="N5" s="168"/>
+      <c r="A5" s="168"/>
+      <c r="B5" s="175"/>
+      <c r="C5" s="168"/>
+      <c r="D5" s="168"/>
+      <c r="E5" s="171"/>
+      <c r="F5" s="168"/>
+      <c r="G5" s="168"/>
+      <c r="H5" s="168"/>
+      <c r="I5" s="171"/>
+      <c r="J5" s="171"/>
+      <c r="K5" s="171"/>
+      <c r="L5" s="168"/>
+      <c r="M5" s="171"/>
+      <c r="N5" s="171"/>
       <c r="O5" s="67" t="str">
         <f>RESUMEN!B9</f>
         <v>VTO 14/07</v>
       </c>
-      <c r="P5" s="166"/>
+      <c r="P5" s="168"/>
     </row>
     <row r="6" spans="1:20" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="5" t="s">
@@ -3781,10 +3790,10 @@
       <c r="F20" s="80">
         <v>5</v>
       </c>
-      <c r="G20" s="81">
+      <c r="G20" s="182">
         <v>132829.16</v>
       </c>
-      <c r="H20" s="82">
+      <c r="H20" s="182">
         <f>118000+5000+1000</f>
         <v>124000</v>
       </c>
@@ -4116,93 +4125,106 @@
     </row>
     <row r="27" spans="1:20" hidden="1" x14ac:dyDescent="0.25"/>
     <row r="28" spans="1:20" ht="9" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="D28" s="161" t="s">
+      <c r="D28" s="160" t="s">
         <v>144</v>
       </c>
-      <c r="E28" s="151"/>
-      <c r="F28" s="151"/>
-      <c r="G28" s="151"/>
-      <c r="H28" s="151"/>
-      <c r="I28" s="151"/>
-      <c r="J28" s="151"/>
-      <c r="K28" s="151"/>
-      <c r="L28" s="151"/>
-      <c r="M28" s="151"/>
-      <c r="N28" s="151"/>
-      <c r="O28" s="151"/>
+      <c r="E28" s="153"/>
+      <c r="F28" s="153"/>
+      <c r="G28" s="153"/>
+      <c r="H28" s="153"/>
+      <c r="I28" s="153"/>
+      <c r="J28" s="153"/>
+      <c r="K28" s="153"/>
+      <c r="L28" s="153"/>
+      <c r="M28" s="153"/>
+      <c r="N28" s="153"/>
+      <c r="O28" s="153"/>
     </row>
     <row r="29" spans="1:20" ht="12" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="D29" s="151"/>
-      <c r="E29" s="151"/>
-      <c r="F29" s="151"/>
-      <c r="G29" s="151"/>
-      <c r="H29" s="151"/>
-      <c r="I29" s="151"/>
-      <c r="J29" s="151"/>
-      <c r="K29" s="151"/>
-      <c r="L29" s="151"/>
-      <c r="M29" s="151"/>
-      <c r="N29" s="151"/>
-      <c r="O29" s="151"/>
+      <c r="D29" s="153"/>
+      <c r="E29" s="153"/>
+      <c r="F29" s="153"/>
+      <c r="G29" s="153"/>
+      <c r="H29" s="153"/>
+      <c r="I29" s="153"/>
+      <c r="J29" s="153"/>
+      <c r="K29" s="153"/>
+      <c r="L29" s="153"/>
+      <c r="M29" s="153"/>
+      <c r="N29" s="153"/>
+      <c r="O29" s="153"/>
     </row>
     <row r="30" spans="1:20" ht="12" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="D30" s="151"/>
-      <c r="E30" s="151"/>
-      <c r="F30" s="151"/>
-      <c r="G30" s="151"/>
-      <c r="H30" s="151"/>
-      <c r="I30" s="151"/>
-      <c r="J30" s="151"/>
-      <c r="K30" s="151"/>
-      <c r="L30" s="151"/>
-      <c r="M30" s="151"/>
-      <c r="N30" s="151"/>
-      <c r="O30" s="151"/>
+      <c r="D30" s="153"/>
+      <c r="E30" s="153"/>
+      <c r="F30" s="153"/>
+      <c r="G30" s="153"/>
+      <c r="H30" s="153"/>
+      <c r="I30" s="153"/>
+      <c r="J30" s="153"/>
+      <c r="K30" s="153"/>
+      <c r="L30" s="153"/>
+      <c r="M30" s="153"/>
+      <c r="N30" s="153"/>
+      <c r="O30" s="153"/>
     </row>
     <row r="31" spans="1:20" ht="12" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="D31" s="151"/>
-      <c r="E31" s="151"/>
-      <c r="F31" s="151"/>
-      <c r="G31" s="151"/>
-      <c r="H31" s="151"/>
-      <c r="I31" s="151"/>
-      <c r="J31" s="151"/>
-      <c r="K31" s="151"/>
-      <c r="L31" s="151"/>
-      <c r="M31" s="151"/>
-      <c r="N31" s="151"/>
-      <c r="O31" s="151"/>
+      <c r="D31" s="153"/>
+      <c r="E31" s="153"/>
+      <c r="F31" s="153"/>
+      <c r="G31" s="153"/>
+      <c r="H31" s="153"/>
+      <c r="I31" s="153"/>
+      <c r="J31" s="153"/>
+      <c r="K31" s="153"/>
+      <c r="L31" s="153"/>
+      <c r="M31" s="153"/>
+      <c r="N31" s="153"/>
+      <c r="O31" s="153"/>
     </row>
     <row r="32" spans="1:20" ht="12" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="D32" s="151"/>
-      <c r="E32" s="151"/>
-      <c r="F32" s="151"/>
-      <c r="G32" s="151"/>
-      <c r="H32" s="151"/>
-      <c r="I32" s="151"/>
-      <c r="J32" s="151"/>
-      <c r="K32" s="151"/>
-      <c r="L32" s="151"/>
-      <c r="M32" s="151"/>
-      <c r="N32" s="151"/>
-      <c r="O32" s="151"/>
-    </row>
-    <row r="33" spans="4:15" ht="65.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="D33" s="151"/>
-      <c r="E33" s="151"/>
-      <c r="F33" s="151"/>
-      <c r="G33" s="151"/>
-      <c r="H33" s="151"/>
-      <c r="I33" s="151"/>
-      <c r="J33" s="151"/>
-      <c r="K33" s="151"/>
-      <c r="L33" s="151"/>
-      <c r="M33" s="151"/>
-      <c r="N33" s="151"/>
-      <c r="O33" s="151"/>
+      <c r="D32" s="153"/>
+      <c r="E32" s="153"/>
+      <c r="F32" s="153"/>
+      <c r="G32" s="153"/>
+      <c r="H32" s="153"/>
+      <c r="I32" s="153"/>
+      <c r="J32" s="153"/>
+      <c r="K32" s="153"/>
+      <c r="L32" s="153"/>
+      <c r="M32" s="153"/>
+      <c r="N32" s="153"/>
+      <c r="O32" s="153"/>
+    </row>
+    <row r="33" spans="4:21" ht="65.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="D33" s="153"/>
+      <c r="E33" s="153"/>
+      <c r="F33" s="153"/>
+      <c r="G33" s="153"/>
+      <c r="H33" s="153"/>
+      <c r="I33" s="153"/>
+      <c r="J33" s="153"/>
+      <c r="K33" s="153"/>
+      <c r="L33" s="153"/>
+      <c r="M33" s="153"/>
+      <c r="N33" s="153"/>
+      <c r="O33" s="153"/>
+      <c r="R33" s="183" t="s">
+        <v>165</v>
+      </c>
+      <c r="S33" s="183"/>
+      <c r="T33" s="183"/>
+      <c r="U33" s="183"/>
     </row>
   </sheetData>
   <mergeCells count="19">
+    <mergeCell ref="D28:O33"/>
+    <mergeCell ref="C4:C5"/>
+    <mergeCell ref="E4:E5"/>
+    <mergeCell ref="F1:O1"/>
+    <mergeCell ref="D4:D5"/>
+    <mergeCell ref="J4:J5"/>
+    <mergeCell ref="L4:L5"/>
     <mergeCell ref="A4:A5"/>
     <mergeCell ref="G4:G5"/>
     <mergeCell ref="I4:I5"/>
@@ -4215,13 +4237,6 @@
     <mergeCell ref="N4:N5"/>
     <mergeCell ref="P4:P5"/>
     <mergeCell ref="O3:P3"/>
-    <mergeCell ref="D28:O33"/>
-    <mergeCell ref="C4:C5"/>
-    <mergeCell ref="E4:E5"/>
-    <mergeCell ref="F1:O1"/>
-    <mergeCell ref="D4:D5"/>
-    <mergeCell ref="J4:J5"/>
-    <mergeCell ref="L4:L5"/>
   </mergeCells>
   <pageMargins left="0.25" right="0.25" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="landscape" r:id="rId1"/>
